--- a/artfynd/A 19260-2025 artfynd.xlsx
+++ b/artfynd/A 19260-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>125265231</v>
+        <v>125264864</v>
       </c>
       <c r="B2" t="n">
-        <v>95705</v>
+        <v>57995</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,41 +687,50 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>2180</v>
+        <v>103018</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Svartvit flugsnappare</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Ficedula hypoleuca</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
+          <t>(Pallas, 1764)</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>par i lämplig häckbiotop</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Stora Saltvik, Stora Saltvik, Sm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>590703</v>
+        <v>590744</v>
       </c>
       <c r="R2" t="n">
-        <v>6353508</v>
+        <v>6353445</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -777,7 +786,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>125266422</v>
+        <v>125265667</v>
       </c>
       <c r="B3" t="n">
         <v>95705</v>
@@ -817,10 +826,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>590574</v>
+        <v>590705</v>
       </c>
       <c r="R3" t="n">
-        <v>6353534</v>
+        <v>6353579</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -867,19 +876,19 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>125268245</v>
+        <v>125264737</v>
       </c>
       <c r="B4" t="n">
         <v>57761</v>
@@ -915,14 +924,14 @@
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Lerbro, Lerbro, Sm</t>
+          <t>Stora Saltvik, Saltvik, Sm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>590069</v>
+        <v>590732</v>
       </c>
       <c r="R4" t="n">
-        <v>6353421</v>
+        <v>6353436</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -981,10 +990,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>125265667</v>
+        <v>125265536</v>
       </c>
       <c r="B5" t="n">
-        <v>95705</v>
+        <v>56856</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -997,37 +1006,46 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>2180</v>
+        <v>100065</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Trana</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Grus grus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Stora Saltvik, Stora Saltvik, Sm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>590705</v>
+        <v>590703</v>
       </c>
       <c r="R5" t="n">
-        <v>6353579</v>
+        <v>6353508</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1071,19 +1089,19 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>125265697</v>
+        <v>125265546</v>
       </c>
       <c r="B6" t="n">
         <v>95705</v>
@@ -1123,13 +1141,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>590620</v>
+        <v>590707</v>
       </c>
       <c r="R6" t="n">
-        <v>6353512</v>
+        <v>6353533</v>
       </c>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1173,19 +1191,19 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>125267976</v>
+        <v>125265697</v>
       </c>
       <c r="B7" t="n">
         <v>95705</v>
@@ -1225,10 +1243,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>590840</v>
+        <v>590620</v>
       </c>
       <c r="R7" t="n">
-        <v>6353566</v>
+        <v>6353512</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1287,10 +1305,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>125267022</v>
+        <v>125266788</v>
       </c>
       <c r="B8" t="n">
-        <v>79428</v>
+        <v>95705</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1299,25 +1317,25 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6453</v>
+        <v>2180</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1327,10 +1345,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>590681</v>
+        <v>590574</v>
       </c>
       <c r="R8" t="n">
-        <v>6353540</v>
+        <v>6353534</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1389,10 +1407,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>125267219</v>
+        <v>125267022</v>
       </c>
       <c r="B9" t="n">
-        <v>95705</v>
+        <v>79428</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1401,25 +1419,25 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>2180</v>
+        <v>6453</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1593,10 +1611,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>125264768</v>
+        <v>125265040</v>
       </c>
       <c r="B11" t="n">
-        <v>57995</v>
+        <v>95705</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1605,25 +1623,25 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>103018</v>
+        <v>2180</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Svartvit flugsnappare</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Ficedula hypoleuca</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Pallas, 1764)</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1633,13 +1651,13 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>590735</v>
+        <v>590703</v>
       </c>
       <c r="R11" t="n">
-        <v>6353466</v>
+        <v>6353508</v>
       </c>
       <c r="S11" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1683,22 +1701,22 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>125267966</v>
+        <v>125267890</v>
       </c>
       <c r="B12" t="n">
-        <v>57761</v>
+        <v>57529</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1711,21 +1729,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>103012</v>
+        <v>100049</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Grönsångare</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Phylloscopus sibilatrix</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Bechstein, 1793)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -1735,7 +1753,7 @@
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
@@ -1750,7 +1768,7 @@
         <v>6353560</v>
       </c>
       <c r="S12" t="n">
-        <v>20</v>
+        <v>40</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1806,10 +1824,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>125264864</v>
+        <v>125267219</v>
       </c>
       <c r="B13" t="n">
-        <v>57995</v>
+        <v>95705</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1818,50 +1836,41 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>103018</v>
+        <v>2180</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Svartvit flugsnappare</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Ficedula hypoleuca</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Pallas, 1764)</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>par i lämplig häckbiotop</t>
-        </is>
-      </c>
+          <t>(Hedw.) Ångstr.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>Stora Saltvik, Stora Saltvik, Sm</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>590744</v>
+        <v>590681</v>
       </c>
       <c r="R13" t="n">
-        <v>6353445</v>
+        <v>6353540</v>
       </c>
       <c r="S13" t="n">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1917,7 +1926,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>125266294</v>
+        <v>125267309</v>
       </c>
       <c r="B14" t="n">
         <v>57995</v>
@@ -1950,7 +1959,11 @@
           <t>(Pallas, 1764)</t>
         </is>
       </c>
-      <c r="I14" t="inlineStr"/>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="M14" t="inlineStr">
         <is>
           <t>spel/sång</t>
@@ -1962,10 +1975,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>590574</v>
+        <v>590681</v>
       </c>
       <c r="R14" t="n">
-        <v>6353534</v>
+        <v>6353540</v>
       </c>
       <c r="S14" t="n">
         <v>30</v>
@@ -2024,10 +2037,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>125265228</v>
+        <v>125265482</v>
       </c>
       <c r="B15" t="n">
-        <v>79428</v>
+        <v>57995</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2040,37 +2053,46 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6453</v>
+        <v>103018</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Svartvit flugsnappare</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Ficedula hypoleuca</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr"/>
+          <t>(Pallas, 1764)</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Stora Saltvik, Stora Saltvik, Sm</t>
+          <t>Stora Saltvik, Saltvik, Sm</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>590685</v>
+        <v>590703</v>
       </c>
       <c r="R15" t="n">
-        <v>6353472</v>
+        <v>6353508</v>
       </c>
       <c r="S15" t="n">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2114,22 +2136,22 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>125267890</v>
+        <v>125267873</v>
       </c>
       <c r="B16" t="n">
-        <v>57529</v>
+        <v>91032</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2142,46 +2164,37 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100049</v>
+        <v>5442</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
           <t>Stora Saltvik, Stora Saltvik, Sm</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>590812</v>
+        <v>590814</v>
       </c>
       <c r="R16" t="n">
-        <v>6353560</v>
+        <v>6353563</v>
       </c>
       <c r="S16" t="n">
-        <v>40</v>
+        <v>10</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2237,10 +2250,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>125264931</v>
+        <v>125268044</v>
       </c>
       <c r="B17" t="n">
-        <v>95423</v>
+        <v>95705</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2253,21 +2266,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>2671</v>
+        <v>2180</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Fällmossa</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Antitrichia curtipendula</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Hedw.) Brid.</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2277,13 +2290,13 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>590731</v>
+        <v>590840</v>
       </c>
       <c r="R17" t="n">
-        <v>6353465</v>
+        <v>6353566</v>
       </c>
       <c r="S17" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2327,22 +2340,22 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>125267873</v>
+        <v>125268245</v>
       </c>
       <c r="B18" t="n">
-        <v>91032</v>
+        <v>57761</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2355,37 +2368,37 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>5442</v>
+        <v>103012</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Grönsångare</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Phylloscopus sibilatrix</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Bechstein, 1793)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Stora Saltvik, Stora Saltvik, Sm</t>
+          <t>Lerbro, Lerbro, Sm</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>590814</v>
+        <v>590069</v>
       </c>
       <c r="R18" t="n">
-        <v>6353563</v>
+        <v>6353421</v>
       </c>
       <c r="S18" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2429,22 +2442,22 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>125268075</v>
+        <v>125265228</v>
       </c>
       <c r="B19" t="n">
-        <v>57948</v>
+        <v>79428</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2457,46 +2470,37 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>102999</v>
+        <v>6453</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Björktrast</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Turdus pilaris</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
           <t>Stora Saltvik, Stora Saltvik, Sm</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>590840</v>
+        <v>590685</v>
       </c>
       <c r="R19" t="n">
-        <v>6353566</v>
+        <v>6353472</v>
       </c>
       <c r="S19" t="n">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2540,22 +2544,22 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>125265047</v>
+        <v>125264931</v>
       </c>
       <c r="B20" t="n">
-        <v>57529</v>
+        <v>95423</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2564,25 +2568,25 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100049</v>
+        <v>2671</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Fällmossa</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Antitrichia curtipendula</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hedw.) Brid.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2592,13 +2596,13 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>590693</v>
+        <v>590731</v>
       </c>
       <c r="R20" t="n">
-        <v>6353472</v>
+        <v>6353465</v>
       </c>
       <c r="S20" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2628,11 +2632,6 @@
       <c r="AA20" t="inlineStr">
         <is>
           <t>2025-05-20</t>
-        </is>
-      </c>
-      <c r="AC20" t="inlineStr">
-        <is>
-          <t>Födosökshack</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2659,10 +2658,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>125265546</v>
+        <v>125264768</v>
       </c>
       <c r="B21" t="n">
-        <v>95705</v>
+        <v>57995</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2671,25 +2670,25 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>2180</v>
+        <v>103018</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Svartvit flugsnappare</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Ficedula hypoleuca</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(Pallas, 1764)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2699,13 +2698,13 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>590707</v>
+        <v>590735</v>
       </c>
       <c r="R21" t="n">
-        <v>6353533</v>
+        <v>6353466</v>
       </c>
       <c r="S21" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2761,10 +2760,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>125265536</v>
+        <v>125267966</v>
       </c>
       <c r="B22" t="n">
-        <v>56856</v>
+        <v>57761</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2773,25 +2772,25 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100065</v>
+        <v>103012</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Trana</t>
+          <t>Grönsångare</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Grus grus</t>
+          <t>Phylloscopus sibilatrix</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Bechstein, 1793)</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
@@ -2810,13 +2809,13 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>590703</v>
+        <v>590812</v>
       </c>
       <c r="R22" t="n">
-        <v>6353508</v>
+        <v>6353560</v>
       </c>
       <c r="S22" t="n">
-        <v>50</v>
+        <v>20</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -2872,10 +2871,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>125267309</v>
+        <v>125265047</v>
       </c>
       <c r="B23" t="n">
-        <v>57995</v>
+        <v>57529</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2888,46 +2887,37 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>103018</v>
+        <v>100049</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Svartvit flugsnappare</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Ficedula hypoleuca</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Pallas, 1764)</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
           <t>Stora Saltvik, Stora Saltvik, Sm</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>590681</v>
+        <v>590693</v>
       </c>
       <c r="R23" t="n">
-        <v>6353540</v>
+        <v>6353472</v>
       </c>
       <c r="S23" t="n">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -2957,6 +2947,11 @@
       <c r="AA23" t="inlineStr">
         <is>
           <t>2025-05-20</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>Födosökshack</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -2971,22 +2966,22 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>125265888</v>
+        <v>125266294</v>
       </c>
       <c r="B24" t="n">
-        <v>57529</v>
+        <v>57995</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -2999,37 +2994,42 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>100049</v>
+        <v>103018</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Svartvit flugsnappare</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Ficedula hypoleuca</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Pallas, 1764)</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="P24" t="inlineStr">
         <is>
           <t>Stora Saltvik, Stora Saltvik, Sm</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>590717</v>
+        <v>590574</v>
       </c>
       <c r="R24" t="n">
-        <v>6353617</v>
+        <v>6353534</v>
       </c>
       <c r="S24" t="n">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3059,11 +3059,6 @@
       <c r="AA24" t="inlineStr">
         <is>
           <t>2025-05-20</t>
-        </is>
-      </c>
-      <c r="AC24" t="inlineStr">
-        <is>
-          <t>Födosökshack</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3078,22 +3073,22 @@
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>125265482</v>
+        <v>125265888</v>
       </c>
       <c r="B25" t="n">
-        <v>57995</v>
+        <v>57529</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3106,46 +3101,37 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>103018</v>
+        <v>100049</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Svartvit flugsnappare</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Ficedula hypoleuca</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Pallas, 1764)</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M25" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Stora Saltvik, Saltvik, Sm</t>
+          <t>Stora Saltvik, Stora Saltvik, Sm</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>590703</v>
+        <v>590717</v>
       </c>
       <c r="R25" t="n">
-        <v>6353508</v>
+        <v>6353617</v>
       </c>
       <c r="S25" t="n">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3175,6 +3161,11 @@
       <c r="AA25" t="inlineStr">
         <is>
           <t>2025-05-20</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>Födosökshack</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3189,22 +3180,22 @@
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>125264737</v>
+        <v>125268075</v>
       </c>
       <c r="B26" t="n">
-        <v>57761</v>
+        <v>57948</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3217,37 +3208,46 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>103012</v>
+        <v>102999</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Grönsångare</t>
+          <t>Björktrast</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Phylloscopus sibilatrix</t>
+          <t>Turdus pilaris</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Bechstein, 1793)</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Stora Saltvik, Saltvik, Sm</t>
+          <t>Stora Saltvik, Stora Saltvik, Sm</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>590732</v>
+        <v>590840</v>
       </c>
       <c r="R26" t="n">
-        <v>6353436</v>
+        <v>6353566</v>
       </c>
       <c r="S26" t="n">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3291,12 +3291,12 @@
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>

--- a/artfynd/A 19260-2025 artfynd.xlsx
+++ b/artfynd/A 19260-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>125264864</v>
+        <v>125267966</v>
       </c>
       <c r="B2" t="n">
-        <v>57995</v>
+        <v>57761</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,31 +691,31 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>103018</v>
+        <v>103012</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Svartvit flugsnappare</t>
+          <t>Grönsångare</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Ficedula hypoleuca</t>
+          <t>Phylloscopus sibilatrix</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Pallas, 1764)</t>
+          <t>(Bechstein, 1793)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>par i lämplig häckbiotop</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -724,13 +724,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>590744</v>
+        <v>590812</v>
       </c>
       <c r="R2" t="n">
-        <v>6353445</v>
+        <v>6353560</v>
       </c>
       <c r="S2" t="n">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -786,7 +786,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>125265667</v>
+        <v>125265697</v>
       </c>
       <c r="B3" t="n">
         <v>95705</v>
@@ -826,10 +826,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>590705</v>
+        <v>590620</v>
       </c>
       <c r="R3" t="n">
-        <v>6353579</v>
+        <v>6353512</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -876,22 +876,22 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>125264737</v>
+        <v>125264768</v>
       </c>
       <c r="B4" t="n">
-        <v>57761</v>
+        <v>57995</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -904,34 +904,34 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>103012</v>
+        <v>103018</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Grönsångare</t>
+          <t>Svartvit flugsnappare</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Phylloscopus sibilatrix</t>
+          <t>Ficedula hypoleuca</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Bechstein, 1793)</t>
+          <t>(Pallas, 1764)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Stora Saltvik, Saltvik, Sm</t>
+          <t>Stora Saltvik, Stora Saltvik, Sm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>590732</v>
+        <v>590735</v>
       </c>
       <c r="R4" t="n">
-        <v>6353436</v>
+        <v>6353466</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -990,10 +990,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>125265536</v>
+        <v>125265482</v>
       </c>
       <c r="B5" t="n">
-        <v>56856</v>
+        <v>57995</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1002,25 +1002,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100065</v>
+        <v>103018</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Trana</t>
+          <t>Svartvit flugsnappare</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Grus grus</t>
+          <t>Ficedula hypoleuca</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Pallas, 1764)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1035,7 +1035,7 @@
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Stora Saltvik, Stora Saltvik, Sm</t>
+          <t>Stora Saltvik, Saltvik, Sm</t>
         </is>
       </c>
       <c r="Q5" t="n">
@@ -1045,7 +1045,7 @@
         <v>6353508</v>
       </c>
       <c r="S5" t="n">
-        <v>50</v>
+        <v>30</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1101,10 +1101,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>125265546</v>
+        <v>125264864</v>
       </c>
       <c r="B6" t="n">
-        <v>95705</v>
+        <v>57995</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1113,41 +1113,50 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>2180</v>
+        <v>103018</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Svartvit flugsnappare</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Ficedula hypoleuca</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
+          <t>(Pallas, 1764)</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>par i lämplig häckbiotop</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Stora Saltvik, Stora Saltvik, Sm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>590707</v>
+        <v>590744</v>
       </c>
       <c r="R6" t="n">
-        <v>6353533</v>
+        <v>6353445</v>
       </c>
       <c r="S6" t="n">
-        <v>15</v>
+        <v>30</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1191,19 +1200,19 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>125265697</v>
+        <v>125268044</v>
       </c>
       <c r="B7" t="n">
         <v>95705</v>
@@ -1243,10 +1252,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>590620</v>
+        <v>590840</v>
       </c>
       <c r="R7" t="n">
-        <v>6353512</v>
+        <v>6353566</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1305,7 +1314,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>125266788</v>
+        <v>125265546</v>
       </c>
       <c r="B8" t="n">
         <v>95705</v>
@@ -1345,13 +1354,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>590574</v>
+        <v>590707</v>
       </c>
       <c r="R8" t="n">
-        <v>6353534</v>
+        <v>6353533</v>
       </c>
       <c r="S8" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1395,22 +1404,22 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>125267022</v>
+        <v>125265536</v>
       </c>
       <c r="B9" t="n">
-        <v>79428</v>
+        <v>56856</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1419,41 +1428,50 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6453</v>
+        <v>100065</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Trana</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Grus grus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Stora Saltvik, Stora Saltvik, Sm</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>590681</v>
+        <v>590703</v>
       </c>
       <c r="R9" t="n">
-        <v>6353540</v>
+        <v>6353508</v>
       </c>
       <c r="S9" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1509,10 +1527,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>125265456</v>
+        <v>125264737</v>
       </c>
       <c r="B10" t="n">
-        <v>95705</v>
+        <v>57761</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1521,41 +1539,41 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>2180</v>
+        <v>103012</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Grönsångare</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Phylloscopus sibilatrix</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(Bechstein, 1793)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Stora Saltvik, Stora Saltvik, Sm</t>
+          <t>Stora Saltvik, Saltvik, Sm</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>590690</v>
+        <v>590732</v>
       </c>
       <c r="R10" t="n">
-        <v>6353521</v>
+        <v>6353436</v>
       </c>
       <c r="S10" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1611,10 +1629,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>125265040</v>
+        <v>125265888</v>
       </c>
       <c r="B11" t="n">
-        <v>95705</v>
+        <v>57529</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1623,25 +1641,25 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>2180</v>
+        <v>100049</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1651,13 +1669,13 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>590703</v>
+        <v>590717</v>
       </c>
       <c r="R11" t="n">
-        <v>6353508</v>
+        <v>6353617</v>
       </c>
       <c r="S11" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1687,6 +1705,11 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-05-20</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Födosökshack</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1701,22 +1724,22 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>125267890</v>
+        <v>125264931</v>
       </c>
       <c r="B12" t="n">
-        <v>57529</v>
+        <v>95423</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1725,50 +1748,41 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100049</v>
+        <v>2671</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Fällmossa</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Antitrichia curtipendula</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
+          <t>(Hedw.) Brid.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
           <t>Stora Saltvik, Stora Saltvik, Sm</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>590812</v>
+        <v>590731</v>
       </c>
       <c r="R12" t="n">
-        <v>6353560</v>
+        <v>6353465</v>
       </c>
       <c r="S12" t="n">
-        <v>40</v>
+        <v>15</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1812,22 +1826,22 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>125267219</v>
+        <v>125268075</v>
       </c>
       <c r="B13" t="n">
-        <v>95705</v>
+        <v>57948</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1836,41 +1850,50 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>2180</v>
+        <v>102999</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Björktrast</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Turdus pilaris</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Stora Saltvik, Stora Saltvik, Sm</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>590681</v>
+        <v>590840</v>
       </c>
       <c r="R13" t="n">
-        <v>6353540</v>
+        <v>6353566</v>
       </c>
       <c r="S13" t="n">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1926,10 +1949,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>125267309</v>
+        <v>125267873</v>
       </c>
       <c r="B14" t="n">
-        <v>57995</v>
+        <v>91032</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1942,46 +1965,37 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>103018</v>
+        <v>5442</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Svartvit flugsnappare</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Ficedula hypoleuca</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Pallas, 1764)</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
           <t>Stora Saltvik, Stora Saltvik, Sm</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>590681</v>
+        <v>590814</v>
       </c>
       <c r="R14" t="n">
-        <v>6353540</v>
+        <v>6353563</v>
       </c>
       <c r="S14" t="n">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2037,10 +2051,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>125265482</v>
+        <v>125267890</v>
       </c>
       <c r="B15" t="n">
-        <v>57995</v>
+        <v>57529</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2053,21 +2067,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>103018</v>
+        <v>100049</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Svartvit flugsnappare</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Ficedula hypoleuca</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Pallas, 1764)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
@@ -2077,22 +2091,22 @@
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Stora Saltvik, Saltvik, Sm</t>
+          <t>Stora Saltvik, Stora Saltvik, Sm</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>590703</v>
+        <v>590812</v>
       </c>
       <c r="R15" t="n">
-        <v>6353508</v>
+        <v>6353560</v>
       </c>
       <c r="S15" t="n">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2148,10 +2162,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>125267873</v>
+        <v>125266422</v>
       </c>
       <c r="B16" t="n">
-        <v>91032</v>
+        <v>95705</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2160,25 +2174,25 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>5442</v>
+        <v>2180</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2188,10 +2202,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>590814</v>
+        <v>590574</v>
       </c>
       <c r="R16" t="n">
-        <v>6353563</v>
+        <v>6353534</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2250,10 +2264,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>125268044</v>
+        <v>125265228</v>
       </c>
       <c r="B17" t="n">
-        <v>95705</v>
+        <v>79428</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2262,25 +2276,25 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>2180</v>
+        <v>6453</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2290,10 +2304,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>590840</v>
+        <v>590685</v>
       </c>
       <c r="R17" t="n">
-        <v>6353566</v>
+        <v>6353472</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2340,22 +2354,22 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>125268245</v>
+        <v>125267309</v>
       </c>
       <c r="B18" t="n">
-        <v>57761</v>
+        <v>57995</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2368,37 +2382,46 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>103012</v>
+        <v>103018</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Grönsångare</t>
+          <t>Svartvit flugsnappare</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Phylloscopus sibilatrix</t>
+          <t>Ficedula hypoleuca</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Bechstein, 1793)</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr"/>
+          <t>(Pallas, 1764)</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Lerbro, Lerbro, Sm</t>
+          <t>Stora Saltvik, Stora Saltvik, Sm</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>590069</v>
+        <v>590681</v>
       </c>
       <c r="R18" t="n">
-        <v>6353421</v>
+        <v>6353540</v>
       </c>
       <c r="S18" t="n">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2442,22 +2465,22 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>125265228</v>
+        <v>125265231</v>
       </c>
       <c r="B19" t="n">
-        <v>79428</v>
+        <v>95705</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2466,25 +2489,25 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6453</v>
+        <v>2180</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2494,10 +2517,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>590685</v>
+        <v>590703</v>
       </c>
       <c r="R19" t="n">
-        <v>6353472</v>
+        <v>6353508</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2544,22 +2567,22 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>125264931</v>
+        <v>125268245</v>
       </c>
       <c r="B20" t="n">
-        <v>95423</v>
+        <v>57761</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2568,41 +2591,41 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>2671</v>
+        <v>103012</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Fällmossa</t>
+          <t>Grönsångare</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Antitrichia curtipendula</t>
+          <t>Phylloscopus sibilatrix</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Hedw.) Brid.</t>
+          <t>(Bechstein, 1793)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Stora Saltvik, Stora Saltvik, Sm</t>
+          <t>Lerbro, Lerbro, Sm</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>590731</v>
+        <v>590069</v>
       </c>
       <c r="R20" t="n">
-        <v>6353465</v>
+        <v>6353421</v>
       </c>
       <c r="S20" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2658,10 +2681,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>125264768</v>
+        <v>125267022</v>
       </c>
       <c r="B21" t="n">
-        <v>57995</v>
+        <v>79428</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2674,21 +2697,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>103018</v>
+        <v>6453</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Svartvit flugsnappare</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Ficedula hypoleuca</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Pallas, 1764)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2698,13 +2721,13 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>590735</v>
+        <v>590681</v>
       </c>
       <c r="R21" t="n">
-        <v>6353466</v>
+        <v>6353540</v>
       </c>
       <c r="S21" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2748,22 +2771,22 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>125267966</v>
+        <v>125265047</v>
       </c>
       <c r="B22" t="n">
-        <v>57761</v>
+        <v>57529</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2776,43 +2799,34 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>103012</v>
+        <v>100049</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Grönsångare</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Phylloscopus sibilatrix</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Bechstein, 1793)</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
           <t>Stora Saltvik, Stora Saltvik, Sm</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>590812</v>
+        <v>590693</v>
       </c>
       <c r="R22" t="n">
-        <v>6353560</v>
+        <v>6353472</v>
       </c>
       <c r="S22" t="n">
         <v>20</v>
@@ -2847,6 +2861,11 @@
           <t>2025-05-20</t>
         </is>
       </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>Födosökshack</t>
+        </is>
+      </c>
       <c r="AD22" t="b">
         <v>0</v>
       </c>
@@ -2859,22 +2878,22 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>125265047</v>
+        <v>125266294</v>
       </c>
       <c r="B23" t="n">
-        <v>57529</v>
+        <v>57995</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2887,37 +2906,42 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100049</v>
+        <v>103018</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Svartvit flugsnappare</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Ficedula hypoleuca</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Pallas, 1764)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="P23" t="inlineStr">
         <is>
           <t>Stora Saltvik, Stora Saltvik, Sm</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>590693</v>
+        <v>590574</v>
       </c>
       <c r="R23" t="n">
-        <v>6353472</v>
+        <v>6353534</v>
       </c>
       <c r="S23" t="n">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -2947,11 +2971,6 @@
       <c r="AA23" t="inlineStr">
         <is>
           <t>2025-05-20</t>
-        </is>
-      </c>
-      <c r="AC23" t="inlineStr">
-        <is>
-          <t>Födosökshack</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -2966,22 +2985,22 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>125266294</v>
+        <v>125267219</v>
       </c>
       <c r="B24" t="n">
-        <v>57995</v>
+        <v>95705</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -2990,46 +3009,41 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>103018</v>
+        <v>2180</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Svartvit flugsnappare</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Ficedula hypoleuca</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Pallas, 1764)</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
-      <c r="M24" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
       <c r="P24" t="inlineStr">
         <is>
           <t>Stora Saltvik, Stora Saltvik, Sm</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>590574</v>
+        <v>590681</v>
       </c>
       <c r="R24" t="n">
-        <v>6353534</v>
+        <v>6353540</v>
       </c>
       <c r="S24" t="n">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3085,10 +3099,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>125265888</v>
+        <v>125265667</v>
       </c>
       <c r="B25" t="n">
-        <v>57529</v>
+        <v>95705</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3097,25 +3111,25 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>100049</v>
+        <v>2180</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3125,13 +3139,13 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>590717</v>
+        <v>590705</v>
       </c>
       <c r="R25" t="n">
-        <v>6353617</v>
+        <v>6353579</v>
       </c>
       <c r="S25" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3161,11 +3175,6 @@
       <c r="AA25" t="inlineStr">
         <is>
           <t>2025-05-20</t>
-        </is>
-      </c>
-      <c r="AC25" t="inlineStr">
-        <is>
-          <t>Födosökshack</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3192,10 +3201,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>125268075</v>
+        <v>125265456</v>
       </c>
       <c r="B26" t="n">
-        <v>57948</v>
+        <v>95705</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3204,50 +3213,41 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>102999</v>
+        <v>2180</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Björktrast</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Turdus pilaris</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M26" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
+          <t>(Hedw.) Ångstr.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
           <t>Stora Saltvik, Stora Saltvik, Sm</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>590840</v>
+        <v>590690</v>
       </c>
       <c r="R26" t="n">
-        <v>6353566</v>
+        <v>6353521</v>
       </c>
       <c r="S26" t="n">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3291,12 +3291,12 @@
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>

--- a/artfynd/A 19260-2025 artfynd.xlsx
+++ b/artfynd/A 19260-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>125267966</v>
+        <v>125265546</v>
       </c>
       <c r="B2" t="n">
-        <v>57761</v>
+        <v>95705</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,50 +687,41 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>103012</v>
+        <v>2180</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Grönsångare</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Phylloscopus sibilatrix</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Bechstein, 1793)</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
+          <t>(Hedw.) Ångstr.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Stora Saltvik, Stora Saltvik, Sm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>590812</v>
+        <v>590707</v>
       </c>
       <c r="R2" t="n">
-        <v>6353560</v>
+        <v>6353533</v>
       </c>
       <c r="S2" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -774,19 +765,19 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>125265697</v>
+        <v>125265231</v>
       </c>
       <c r="B3" t="n">
         <v>95705</v>
@@ -826,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>590620</v>
+        <v>590703</v>
       </c>
       <c r="R3" t="n">
-        <v>6353512</v>
+        <v>6353508</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -888,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>125264768</v>
+        <v>125265697</v>
       </c>
       <c r="B4" t="n">
-        <v>57995</v>
+        <v>95705</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -900,25 +891,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>103018</v>
+        <v>2180</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Svartvit flugsnappare</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Ficedula hypoleuca</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Pallas, 1764)</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -928,13 +919,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>590735</v>
+        <v>590620</v>
       </c>
       <c r="R4" t="n">
-        <v>6353466</v>
+        <v>6353512</v>
       </c>
       <c r="S4" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -978,22 +969,22 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>125265482</v>
+        <v>125267966</v>
       </c>
       <c r="B5" t="n">
-        <v>57995</v>
+        <v>57761</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1006,21 +997,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>103018</v>
+        <v>103012</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Svartvit flugsnappare</t>
+          <t>Grönsångare</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Ficedula hypoleuca</t>
+          <t>Phylloscopus sibilatrix</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Pallas, 1764)</t>
+          <t>(Bechstein, 1793)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1035,17 +1026,17 @@
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Stora Saltvik, Saltvik, Sm</t>
+          <t>Stora Saltvik, Stora Saltvik, Sm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>590703</v>
+        <v>590812</v>
       </c>
       <c r="R5" t="n">
-        <v>6353508</v>
+        <v>6353560</v>
       </c>
       <c r="S5" t="n">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1101,10 +1092,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>125264864</v>
+        <v>125267219</v>
       </c>
       <c r="B6" t="n">
-        <v>57995</v>
+        <v>95705</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1113,50 +1104,41 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>103018</v>
+        <v>2180</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Svartvit flugsnappare</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Ficedula hypoleuca</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Pallas, 1764)</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>par i lämplig häckbiotop</t>
-        </is>
-      </c>
+          <t>(Hedw.) Ångstr.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Stora Saltvik, Stora Saltvik, Sm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>590744</v>
+        <v>590681</v>
       </c>
       <c r="R6" t="n">
-        <v>6353445</v>
+        <v>6353540</v>
       </c>
       <c r="S6" t="n">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1212,7 +1194,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>125268044</v>
+        <v>125266422</v>
       </c>
       <c r="B7" t="n">
         <v>95705</v>
@@ -1252,10 +1234,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>590840</v>
+        <v>590574</v>
       </c>
       <c r="R7" t="n">
-        <v>6353566</v>
+        <v>6353534</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1314,10 +1296,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>125265546</v>
+        <v>125264768</v>
       </c>
       <c r="B8" t="n">
-        <v>95705</v>
+        <v>57995</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1326,25 +1308,25 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>2180</v>
+        <v>103018</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Svartvit flugsnappare</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Ficedula hypoleuca</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(Pallas, 1764)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1354,13 +1336,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>590707</v>
+        <v>590735</v>
       </c>
       <c r="R8" t="n">
-        <v>6353533</v>
+        <v>6353466</v>
       </c>
       <c r="S8" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1416,10 +1398,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>125265536</v>
+        <v>125265888</v>
       </c>
       <c r="B9" t="n">
-        <v>56856</v>
+        <v>57529</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1428,20 +1410,20 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100065</v>
+        <v>100049</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Trana</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Grus grus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -1449,29 +1431,20 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
+      <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Stora Saltvik, Stora Saltvik, Sm</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>590703</v>
+        <v>590717</v>
       </c>
       <c r="R9" t="n">
-        <v>6353508</v>
+        <v>6353617</v>
       </c>
       <c r="S9" t="n">
-        <v>50</v>
+        <v>20</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1501,6 +1474,11 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-05-20</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Födosökshack</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1515,22 +1493,22 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>125264737</v>
+        <v>125268075</v>
       </c>
       <c r="B10" t="n">
-        <v>57761</v>
+        <v>57948</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1543,37 +1521,46 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>103012</v>
+        <v>102999</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Grönsångare</t>
+          <t>Björktrast</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Phylloscopus sibilatrix</t>
+          <t>Turdus pilaris</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Bechstein, 1793)</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Stora Saltvik, Saltvik, Sm</t>
+          <t>Stora Saltvik, Stora Saltvik, Sm</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>590732</v>
+        <v>590840</v>
       </c>
       <c r="R10" t="n">
-        <v>6353436</v>
+        <v>6353566</v>
       </c>
       <c r="S10" t="n">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1617,22 +1604,22 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>125265888</v>
+        <v>125268044</v>
       </c>
       <c r="B11" t="n">
-        <v>57529</v>
+        <v>95705</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1641,25 +1628,25 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100049</v>
+        <v>2180</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1669,13 +1656,13 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>590717</v>
+        <v>590840</v>
       </c>
       <c r="R11" t="n">
-        <v>6353617</v>
+        <v>6353566</v>
       </c>
       <c r="S11" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1705,11 +1692,6 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-05-20</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>Födosökshack</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1724,12 +1706,12 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
@@ -1838,10 +1820,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>125268075</v>
+        <v>125266294</v>
       </c>
       <c r="B13" t="n">
-        <v>57948</v>
+        <v>57995</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1854,31 +1836,27 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>102999</v>
+        <v>103018</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Björktrast</t>
+          <t>Svartvit flugsnappare</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Turdus pilaris</t>
+          <t>Ficedula hypoleuca</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Pallas, 1764)</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
       <c r="M13" t="inlineStr">
         <is>
-          <t>upprörd, varnande</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
@@ -1887,10 +1865,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>590840</v>
+        <v>590574</v>
       </c>
       <c r="R13" t="n">
-        <v>6353566</v>
+        <v>6353534</v>
       </c>
       <c r="S13" t="n">
         <v>30</v>
@@ -1949,10 +1927,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>125267873</v>
+        <v>125268245</v>
       </c>
       <c r="B14" t="n">
-        <v>91032</v>
+        <v>57761</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1965,37 +1943,37 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>5442</v>
+        <v>103012</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Grönsångare</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Phylloscopus sibilatrix</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Bechstein, 1793)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Stora Saltvik, Stora Saltvik, Sm</t>
+          <t>Lerbro, Lerbro, Sm</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>590814</v>
+        <v>590069</v>
       </c>
       <c r="R14" t="n">
-        <v>6353563</v>
+        <v>6353421</v>
       </c>
       <c r="S14" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2039,19 +2017,19 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>125267890</v>
+        <v>125265047</v>
       </c>
       <c r="B15" t="n">
         <v>57529</v>
@@ -2084,29 +2062,20 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
+      <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
           <t>Stora Saltvik, Stora Saltvik, Sm</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>590812</v>
+        <v>590693</v>
       </c>
       <c r="R15" t="n">
-        <v>6353560</v>
+        <v>6353472</v>
       </c>
       <c r="S15" t="n">
-        <v>40</v>
+        <v>20</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2136,6 +2105,11 @@
       <c r="AA15" t="inlineStr">
         <is>
           <t>2025-05-20</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Födosökshack</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2150,22 +2124,22 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>125266422</v>
+        <v>125267873</v>
       </c>
       <c r="B16" t="n">
-        <v>95705</v>
+        <v>91032</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2174,25 +2148,25 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>2180</v>
+        <v>5442</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2202,10 +2176,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>590574</v>
+        <v>590814</v>
       </c>
       <c r="R16" t="n">
-        <v>6353534</v>
+        <v>6353563</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2366,10 +2340,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>125267309</v>
+        <v>125264737</v>
       </c>
       <c r="B18" t="n">
-        <v>57995</v>
+        <v>57761</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2382,46 +2356,37 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>103018</v>
+        <v>103012</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Svartvit flugsnappare</t>
+          <t>Grönsångare</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Ficedula hypoleuca</t>
+          <t>Phylloscopus sibilatrix</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Pallas, 1764)</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
+          <t>(Bechstein, 1793)</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Stora Saltvik, Stora Saltvik, Sm</t>
+          <t>Stora Saltvik, Saltvik, Sm</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>590681</v>
+        <v>590732</v>
       </c>
       <c r="R18" t="n">
-        <v>6353540</v>
+        <v>6353436</v>
       </c>
       <c r="S18" t="n">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2465,22 +2430,22 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>125265231</v>
+        <v>125267890</v>
       </c>
       <c r="B19" t="n">
-        <v>95705</v>
+        <v>57529</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2489,41 +2454,50 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>2180</v>
+        <v>100049</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="P19" t="inlineStr">
         <is>
           <t>Stora Saltvik, Stora Saltvik, Sm</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>590703</v>
+        <v>590812</v>
       </c>
       <c r="R19" t="n">
-        <v>6353508</v>
+        <v>6353560</v>
       </c>
       <c r="S19" t="n">
-        <v>10</v>
+        <v>40</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2579,10 +2553,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>125268245</v>
+        <v>125265482</v>
       </c>
       <c r="B20" t="n">
-        <v>57761</v>
+        <v>57995</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2595,37 +2569,46 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>103012</v>
+        <v>103018</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Grönsångare</t>
+          <t>Svartvit flugsnappare</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Phylloscopus sibilatrix</t>
+          <t>Ficedula hypoleuca</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Bechstein, 1793)</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr"/>
+          <t>(Pallas, 1764)</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Lerbro, Lerbro, Sm</t>
+          <t>Stora Saltvik, Saltvik, Sm</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>590069</v>
+        <v>590703</v>
       </c>
       <c r="R20" t="n">
-        <v>6353421</v>
+        <v>6353508</v>
       </c>
       <c r="S20" t="n">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2669,22 +2652,22 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>125267022</v>
+        <v>125267309</v>
       </c>
       <c r="B21" t="n">
-        <v>79428</v>
+        <v>57995</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2697,24 +2680,33 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6453</v>
+        <v>103018</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Svartvit flugsnappare</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Ficedula hypoleuca</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr"/>
+          <t>(Pallas, 1764)</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="P21" t="inlineStr">
         <is>
           <t>Stora Saltvik, Stora Saltvik, Sm</t>
@@ -2727,7 +2719,7 @@
         <v>6353540</v>
       </c>
       <c r="S21" t="n">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2783,10 +2775,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>125265047</v>
+        <v>125267022</v>
       </c>
       <c r="B22" t="n">
-        <v>57529</v>
+        <v>79428</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2799,21 +2791,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100049</v>
+        <v>6453</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2823,13 +2815,13 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>590693</v>
+        <v>590681</v>
       </c>
       <c r="R22" t="n">
-        <v>6353472</v>
+        <v>6353540</v>
       </c>
       <c r="S22" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -2859,11 +2851,6 @@
       <c r="AA22" t="inlineStr">
         <is>
           <t>2025-05-20</t>
-        </is>
-      </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>Födosökshack</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2878,22 +2865,22 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>125266294</v>
+        <v>125265536</v>
       </c>
       <c r="B23" t="n">
-        <v>57995</v>
+        <v>56856</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2902,28 +2889,32 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>103018</v>
+        <v>100065</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Svartvit flugsnappare</t>
+          <t>Trana</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Ficedula hypoleuca</t>
+          <t>Grus grus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Pallas, 1764)</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="M23" t="inlineStr">
         <is>
           <t>spel/sång</t>
@@ -2935,13 +2926,13 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>590574</v>
+        <v>590703</v>
       </c>
       <c r="R23" t="n">
-        <v>6353534</v>
+        <v>6353508</v>
       </c>
       <c r="S23" t="n">
-        <v>30</v>
+        <v>50</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -2997,10 +2988,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>125267219</v>
+        <v>125264864</v>
       </c>
       <c r="B24" t="n">
-        <v>95705</v>
+        <v>57995</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3009,41 +3000,50 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>2180</v>
+        <v>103018</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Svartvit flugsnappare</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Ficedula hypoleuca</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr"/>
+          <t>(Pallas, 1764)</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>par i lämplig häckbiotop</t>
+        </is>
+      </c>
       <c r="P24" t="inlineStr">
         <is>
           <t>Stora Saltvik, Stora Saltvik, Sm</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>590681</v>
+        <v>590744</v>
       </c>
       <c r="R24" t="n">
-        <v>6353540</v>
+        <v>6353445</v>
       </c>
       <c r="S24" t="n">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3099,7 +3099,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>125265667</v>
+        <v>125265456</v>
       </c>
       <c r="B25" t="n">
         <v>95705</v>
@@ -3139,13 +3139,13 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>590705</v>
+        <v>590690</v>
       </c>
       <c r="R25" t="n">
-        <v>6353579</v>
+        <v>6353521</v>
       </c>
       <c r="S25" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3201,7 +3201,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>125265456</v>
+        <v>125265667</v>
       </c>
       <c r="B26" t="n">
         <v>95705</v>
@@ -3241,13 +3241,13 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>590690</v>
+        <v>590705</v>
       </c>
       <c r="R26" t="n">
-        <v>6353521</v>
+        <v>6353579</v>
       </c>
       <c r="S26" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>

--- a/artfynd/A 19260-2025 artfynd.xlsx
+++ b/artfynd/A 19260-2025 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>125265546</v>
+        <v>125265231</v>
       </c>
       <c r="B2" t="n">
         <v>95705</v>
@@ -715,13 +715,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>590707</v>
+        <v>590703</v>
       </c>
       <c r="R2" t="n">
-        <v>6353533</v>
+        <v>6353508</v>
       </c>
       <c r="S2" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -765,19 +765,19 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>125265231</v>
+        <v>125265546</v>
       </c>
       <c r="B3" t="n">
         <v>95705</v>
@@ -817,13 +817,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>590703</v>
+        <v>590707</v>
       </c>
       <c r="R3" t="n">
-        <v>6353508</v>
+        <v>6353533</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -867,12 +867,12 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
@@ -981,10 +981,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>125267966</v>
+        <v>125267219</v>
       </c>
       <c r="B5" t="n">
-        <v>57761</v>
+        <v>95705</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -993,50 +993,41 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>103012</v>
+        <v>2180</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Grönsångare</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Phylloscopus sibilatrix</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Bechstein, 1793)</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
+          <t>(Hedw.) Ångstr.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Stora Saltvik, Stora Saltvik, Sm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>590812</v>
+        <v>590681</v>
       </c>
       <c r="R5" t="n">
-        <v>6353560</v>
+        <v>6353540</v>
       </c>
       <c r="S5" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1092,10 +1083,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>125267219</v>
+        <v>125267966</v>
       </c>
       <c r="B6" t="n">
-        <v>95705</v>
+        <v>57761</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1104,41 +1095,50 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>2180</v>
+        <v>103012</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Grönsångare</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Phylloscopus sibilatrix</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
+          <t>(Bechstein, 1793)</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Stora Saltvik, Stora Saltvik, Sm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>590681</v>
+        <v>590812</v>
       </c>
       <c r="R6" t="n">
-        <v>6353540</v>
+        <v>6353560</v>
       </c>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -2877,10 +2877,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>125265536</v>
+        <v>125264864</v>
       </c>
       <c r="B23" t="n">
-        <v>56856</v>
+        <v>57995</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2889,35 +2889,35 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100065</v>
+        <v>103018</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Trana</t>
+          <t>Svartvit flugsnappare</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Grus grus</t>
+          <t>Ficedula hypoleuca</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Pallas, 1764)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>par i lämplig häckbiotop</t>
         </is>
       </c>
       <c r="P23" t="inlineStr">
@@ -2926,13 +2926,13 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>590703</v>
+        <v>590744</v>
       </c>
       <c r="R23" t="n">
-        <v>6353508</v>
+        <v>6353445</v>
       </c>
       <c r="S23" t="n">
-        <v>50</v>
+        <v>30</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -2988,10 +2988,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>125264864</v>
+        <v>125265536</v>
       </c>
       <c r="B24" t="n">
-        <v>57995</v>
+        <v>56856</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3000,35 +3000,35 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>103018</v>
+        <v>100065</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Svartvit flugsnappare</t>
+          <t>Trana</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Ficedula hypoleuca</t>
+          <t>Grus grus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Pallas, 1764)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>par i lämplig häckbiotop</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="P24" t="inlineStr">
@@ -3037,13 +3037,13 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>590744</v>
+        <v>590703</v>
       </c>
       <c r="R24" t="n">
-        <v>6353445</v>
+        <v>6353508</v>
       </c>
       <c r="S24" t="n">
-        <v>30</v>
+        <v>50</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>

--- a/artfynd/A 19260-2025 artfynd.xlsx
+++ b/artfynd/A 19260-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>125265231</v>
+        <v>125265047</v>
       </c>
       <c r="B2" t="n">
-        <v>95705</v>
+        <v>57529</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>2180</v>
+        <v>100049</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,13 +715,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>590703</v>
+        <v>590693</v>
       </c>
       <c r="R2" t="n">
-        <v>6353508</v>
+        <v>6353472</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -751,6 +751,11 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2025-05-20</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Födosökshack</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -765,12 +770,12 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
@@ -879,10 +884,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>125265697</v>
+        <v>125267873</v>
       </c>
       <c r="B4" t="n">
-        <v>95705</v>
+        <v>91032</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -891,25 +896,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>2180</v>
+        <v>5442</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -919,10 +924,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>590620</v>
+        <v>590814</v>
       </c>
       <c r="R4" t="n">
-        <v>6353512</v>
+        <v>6353563</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -981,7 +986,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>125267219</v>
+        <v>125266788</v>
       </c>
       <c r="B5" t="n">
         <v>95705</v>
@@ -1021,10 +1026,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>590681</v>
+        <v>590574</v>
       </c>
       <c r="R5" t="n">
-        <v>6353540</v>
+        <v>6353534</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1083,10 +1088,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>125267966</v>
+        <v>125265888</v>
       </c>
       <c r="B6" t="n">
-        <v>57761</v>
+        <v>57529</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1099,43 +1104,34 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>103012</v>
+        <v>100049</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Grönsångare</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Phylloscopus sibilatrix</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Bechstein, 1793)</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Stora Saltvik, Stora Saltvik, Sm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>590812</v>
+        <v>590717</v>
       </c>
       <c r="R6" t="n">
-        <v>6353560</v>
+        <v>6353617</v>
       </c>
       <c r="S6" t="n">
         <v>20</v>
@@ -1170,6 +1166,11 @@
           <t>2025-05-20</t>
         </is>
       </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Födosökshack</t>
+        </is>
+      </c>
       <c r="AD6" t="b">
         <v>0</v>
       </c>
@@ -1182,19 +1183,19 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>125266422</v>
+        <v>125265581</v>
       </c>
       <c r="B7" t="n">
         <v>95705</v>
@@ -1234,10 +1235,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>590574</v>
+        <v>590620</v>
       </c>
       <c r="R7" t="n">
-        <v>6353534</v>
+        <v>6353512</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1296,10 +1297,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>125264768</v>
+        <v>125265536</v>
       </c>
       <c r="B8" t="n">
-        <v>57995</v>
+        <v>56856</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1308,41 +1309,50 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>103018</v>
+        <v>100065</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Svartvit flugsnappare</t>
+          <t>Trana</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Ficedula hypoleuca</t>
+          <t>Grus grus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Pallas, 1764)</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Stora Saltvik, Stora Saltvik, Sm</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>590735</v>
+        <v>590703</v>
       </c>
       <c r="R8" t="n">
-        <v>6353466</v>
+        <v>6353508</v>
       </c>
       <c r="S8" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1386,22 +1396,22 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>125265888</v>
+        <v>125268245</v>
       </c>
       <c r="B9" t="n">
-        <v>57529</v>
+        <v>57761</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1414,37 +1424,37 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100049</v>
+        <v>103012</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Grönsångare</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Phylloscopus sibilatrix</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Bechstein, 1793)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Stora Saltvik, Stora Saltvik, Sm</t>
+          <t>Lerbro, Lerbro, Sm</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>590717</v>
+        <v>590069</v>
       </c>
       <c r="R9" t="n">
-        <v>6353617</v>
+        <v>6353421</v>
       </c>
       <c r="S9" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1474,11 +1484,6 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-05-20</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Födosökshack</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1505,10 +1510,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>125268075</v>
+        <v>125265482</v>
       </c>
       <c r="B10" t="n">
-        <v>57948</v>
+        <v>57995</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1521,21 +1526,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>102999</v>
+        <v>103018</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Björktrast</t>
+          <t>Svartvit flugsnappare</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Turdus pilaris</t>
+          <t>Ficedula hypoleuca</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Pallas, 1764)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -1545,19 +1550,19 @@
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>upprörd, varnande</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Stora Saltvik, Stora Saltvik, Sm</t>
+          <t>Stora Saltvik, Saltvik, Sm</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>590840</v>
+        <v>590703</v>
       </c>
       <c r="R10" t="n">
-        <v>6353566</v>
+        <v>6353508</v>
       </c>
       <c r="S10" t="n">
         <v>30</v>
@@ -1616,10 +1621,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>125268044</v>
+        <v>125264931</v>
       </c>
       <c r="B11" t="n">
-        <v>95705</v>
+        <v>95423</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1632,21 +1637,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>2180</v>
+        <v>2671</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Fällmossa</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Antitrichia curtipendula</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(Hedw.) Brid.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1656,13 +1661,13 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>590840</v>
+        <v>590731</v>
       </c>
       <c r="R11" t="n">
-        <v>6353566</v>
+        <v>6353465</v>
       </c>
       <c r="S11" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1706,22 +1711,22 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>125264931</v>
+        <v>125267309</v>
       </c>
       <c r="B12" t="n">
-        <v>95423</v>
+        <v>57995</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1730,41 +1735,50 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>2671</v>
+        <v>103018</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Fällmossa</t>
+          <t>Svartvit flugsnappare</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Antitrichia curtipendula</t>
+          <t>Ficedula hypoleuca</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Hedw.) Brid.</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr"/>
+          <t>(Pallas, 1764)</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Stora Saltvik, Stora Saltvik, Sm</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>590731</v>
+        <v>590681</v>
       </c>
       <c r="R12" t="n">
-        <v>6353465</v>
+        <v>6353540</v>
       </c>
       <c r="S12" t="n">
-        <v>15</v>
+        <v>30</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1808,22 +1822,22 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>125266294</v>
+        <v>125265231</v>
       </c>
       <c r="B13" t="n">
-        <v>57995</v>
+        <v>95705</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1832,46 +1846,41 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>103018</v>
+        <v>2180</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Svartvit flugsnappare</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Ficedula hypoleuca</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Pallas, 1764)</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Stora Saltvik, Stora Saltvik, Sm</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>590574</v>
+        <v>590703</v>
       </c>
       <c r="R13" t="n">
-        <v>6353534</v>
+        <v>6353508</v>
       </c>
       <c r="S13" t="n">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1927,10 +1936,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>125268245</v>
+        <v>125265667</v>
       </c>
       <c r="B14" t="n">
-        <v>57761</v>
+        <v>95705</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1939,41 +1948,41 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>103012</v>
+        <v>2180</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Grönsångare</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Phylloscopus sibilatrix</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Bechstein, 1793)</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Lerbro, Lerbro, Sm</t>
+          <t>Stora Saltvik, Stora Saltvik, Sm</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>590069</v>
+        <v>590705</v>
       </c>
       <c r="R14" t="n">
-        <v>6353421</v>
+        <v>6353579</v>
       </c>
       <c r="S14" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2029,10 +2038,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>125265047</v>
+        <v>125266294</v>
       </c>
       <c r="B15" t="n">
-        <v>57529</v>
+        <v>57995</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2045,37 +2054,42 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100049</v>
+        <v>103018</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Svartvit flugsnappare</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Ficedula hypoleuca</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Pallas, 1764)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="P15" t="inlineStr">
         <is>
           <t>Stora Saltvik, Stora Saltvik, Sm</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>590693</v>
+        <v>590574</v>
       </c>
       <c r="R15" t="n">
-        <v>6353472</v>
+        <v>6353534</v>
       </c>
       <c r="S15" t="n">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2105,11 +2119,6 @@
       <c r="AA15" t="inlineStr">
         <is>
           <t>2025-05-20</t>
-        </is>
-      </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>Födosökshack</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2124,22 +2133,22 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>125267873</v>
+        <v>125267219</v>
       </c>
       <c r="B16" t="n">
-        <v>91032</v>
+        <v>95705</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2148,25 +2157,25 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>5442</v>
+        <v>2180</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2176,10 +2185,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>590814</v>
+        <v>590681</v>
       </c>
       <c r="R16" t="n">
-        <v>6353563</v>
+        <v>6353540</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2238,10 +2247,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>125265228</v>
+        <v>125265456</v>
       </c>
       <c r="B17" t="n">
-        <v>79428</v>
+        <v>95705</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2250,25 +2259,25 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6453</v>
+        <v>2180</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2278,13 +2287,13 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>590685</v>
+        <v>590690</v>
       </c>
       <c r="R17" t="n">
-        <v>6353472</v>
+        <v>6353521</v>
       </c>
       <c r="S17" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2340,10 +2349,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>125264737</v>
+        <v>125264864</v>
       </c>
       <c r="B18" t="n">
-        <v>57761</v>
+        <v>57995</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2356,37 +2365,46 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>103012</v>
+        <v>103018</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Grönsångare</t>
+          <t>Svartvit flugsnappare</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Phylloscopus sibilatrix</t>
+          <t>Ficedula hypoleuca</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Bechstein, 1793)</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr"/>
+          <t>(Pallas, 1764)</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>par i lämplig häckbiotop</t>
+        </is>
+      </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Stora Saltvik, Saltvik, Sm</t>
+          <t>Stora Saltvik, Stora Saltvik, Sm</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>590732</v>
+        <v>590744</v>
       </c>
       <c r="R18" t="n">
-        <v>6353436</v>
+        <v>6353445</v>
       </c>
       <c r="S18" t="n">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2430,22 +2448,22 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>125267890</v>
+        <v>125264768</v>
       </c>
       <c r="B19" t="n">
-        <v>57529</v>
+        <v>57995</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2458,46 +2476,37 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100049</v>
+        <v>103018</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Svartvit flugsnappare</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Ficedula hypoleuca</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
+          <t>(Pallas, 1764)</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
           <t>Stora Saltvik, Stora Saltvik, Sm</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>590812</v>
+        <v>590735</v>
       </c>
       <c r="R19" t="n">
-        <v>6353560</v>
+        <v>6353466</v>
       </c>
       <c r="S19" t="n">
-        <v>40</v>
+        <v>25</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2541,22 +2550,22 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>125265482</v>
+        <v>125267890</v>
       </c>
       <c r="B20" t="n">
-        <v>57995</v>
+        <v>57529</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2569,21 +2578,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>103018</v>
+        <v>100049</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Svartvit flugsnappare</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Ficedula hypoleuca</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Pallas, 1764)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
@@ -2593,22 +2602,22 @@
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Stora Saltvik, Saltvik, Sm</t>
+          <t>Stora Saltvik, Stora Saltvik, Sm</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>590703</v>
+        <v>590812</v>
       </c>
       <c r="R20" t="n">
-        <v>6353508</v>
+        <v>6353560</v>
       </c>
       <c r="S20" t="n">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2664,10 +2673,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>125267309</v>
+        <v>125268075</v>
       </c>
       <c r="B21" t="n">
-        <v>57995</v>
+        <v>57948</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2680,21 +2689,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>103018</v>
+        <v>102999</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Svartvit flugsnappare</t>
+          <t>Björktrast</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Ficedula hypoleuca</t>
+          <t>Turdus pilaris</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Pallas, 1764)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
@@ -2704,7 +2713,7 @@
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>upprörd, varnande</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
@@ -2713,10 +2722,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>590681</v>
+        <v>590840</v>
       </c>
       <c r="R21" t="n">
-        <v>6353540</v>
+        <v>6353566</v>
       </c>
       <c r="S21" t="n">
         <v>30</v>
@@ -2775,10 +2784,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>125267022</v>
+        <v>125268044</v>
       </c>
       <c r="B22" t="n">
-        <v>79428</v>
+        <v>95705</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2787,25 +2796,25 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6453</v>
+        <v>2180</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2815,10 +2824,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>590681</v>
+        <v>590840</v>
       </c>
       <c r="R22" t="n">
-        <v>6353540</v>
+        <v>6353566</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2877,10 +2886,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>125264864</v>
+        <v>125265228</v>
       </c>
       <c r="B23" t="n">
-        <v>57995</v>
+        <v>79428</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2893,46 +2902,37 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>103018</v>
+        <v>6453</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Svartvit flugsnappare</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Ficedula hypoleuca</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Pallas, 1764)</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>par i lämplig häckbiotop</t>
-        </is>
-      </c>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
           <t>Stora Saltvik, Stora Saltvik, Sm</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>590744</v>
+        <v>590685</v>
       </c>
       <c r="R23" t="n">
-        <v>6353445</v>
+        <v>6353472</v>
       </c>
       <c r="S23" t="n">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -2976,22 +2976,22 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>125265536</v>
+        <v>125267966</v>
       </c>
       <c r="B24" t="n">
-        <v>56856</v>
+        <v>57761</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3000,25 +3000,25 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>100065</v>
+        <v>103012</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Trana</t>
+          <t>Grönsångare</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Grus grus</t>
+          <t>Phylloscopus sibilatrix</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Bechstein, 1793)</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
@@ -3037,13 +3037,13 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>590703</v>
+        <v>590812</v>
       </c>
       <c r="R24" t="n">
-        <v>6353508</v>
+        <v>6353560</v>
       </c>
       <c r="S24" t="n">
-        <v>50</v>
+        <v>20</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3099,10 +3099,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>125265456</v>
+        <v>125267022</v>
       </c>
       <c r="B25" t="n">
-        <v>95705</v>
+        <v>79428</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3111,25 +3111,25 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>2180</v>
+        <v>6453</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3139,13 +3139,13 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>590690</v>
+        <v>590681</v>
       </c>
       <c r="R25" t="n">
-        <v>6353521</v>
+        <v>6353540</v>
       </c>
       <c r="S25" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3189,22 +3189,22 @@
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>125265667</v>
+        <v>125264737</v>
       </c>
       <c r="B26" t="n">
-        <v>95705</v>
+        <v>57761</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3213,41 +3213,41 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>2180</v>
+        <v>103012</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Grönsångare</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Phylloscopus sibilatrix</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(Bechstein, 1793)</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Stora Saltvik, Stora Saltvik, Sm</t>
+          <t>Stora Saltvik, Saltvik, Sm</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>590705</v>
+        <v>590732</v>
       </c>
       <c r="R26" t="n">
-        <v>6353579</v>
+        <v>6353436</v>
       </c>
       <c r="S26" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>

--- a/artfynd/A 19260-2025 artfynd.xlsx
+++ b/artfynd/A 19260-2025 artfynd.xlsx
@@ -1297,10 +1297,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>125265536</v>
+        <v>125268245</v>
       </c>
       <c r="B8" t="n">
-        <v>56856</v>
+        <v>57761</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1309,50 +1309,41 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100065</v>
+        <v>103012</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Trana</t>
+          <t>Grönsångare</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Grus grus</t>
+          <t>Phylloscopus sibilatrix</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
+          <t>(Bechstein, 1793)</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Stora Saltvik, Stora Saltvik, Sm</t>
+          <t>Lerbro, Lerbro, Sm</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>590703</v>
+        <v>590069</v>
       </c>
       <c r="R8" t="n">
-        <v>6353508</v>
+        <v>6353421</v>
       </c>
       <c r="S8" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1396,22 +1387,22 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>125268245</v>
+        <v>125265536</v>
       </c>
       <c r="B9" t="n">
-        <v>57761</v>
+        <v>56856</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1420,41 +1411,50 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>103012</v>
+        <v>100065</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Grönsångare</t>
+          <t>Trana</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Phylloscopus sibilatrix</t>
+          <t>Grus grus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Bechstein, 1793)</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Lerbro, Lerbro, Sm</t>
+          <t>Stora Saltvik, Stora Saltvik, Sm</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>590069</v>
+        <v>590703</v>
       </c>
       <c r="R9" t="n">
-        <v>6353421</v>
+        <v>6353508</v>
       </c>
       <c r="S9" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1498,12 +1498,12 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
@@ -2145,10 +2145,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>125267219</v>
+        <v>125264864</v>
       </c>
       <c r="B16" t="n">
-        <v>95705</v>
+        <v>57995</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2157,41 +2157,50 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>2180</v>
+        <v>103018</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Svartvit flugsnappare</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Ficedula hypoleuca</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr"/>
+          <t>(Pallas, 1764)</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>par i lämplig häckbiotop</t>
+        </is>
+      </c>
       <c r="P16" t="inlineStr">
         <is>
           <t>Stora Saltvik, Stora Saltvik, Sm</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>590681</v>
+        <v>590744</v>
       </c>
       <c r="R16" t="n">
-        <v>6353540</v>
+        <v>6353445</v>
       </c>
       <c r="S16" t="n">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2247,10 +2256,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>125265456</v>
+        <v>125264768</v>
       </c>
       <c r="B17" t="n">
-        <v>95705</v>
+        <v>57995</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2259,25 +2268,25 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>2180</v>
+        <v>103018</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Svartvit flugsnappare</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Ficedula hypoleuca</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(Pallas, 1764)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2287,13 +2296,13 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>590690</v>
+        <v>590735</v>
       </c>
       <c r="R17" t="n">
-        <v>6353521</v>
+        <v>6353466</v>
       </c>
       <c r="S17" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2349,10 +2358,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>125264864</v>
+        <v>125267219</v>
       </c>
       <c r="B18" t="n">
-        <v>57995</v>
+        <v>95705</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2361,50 +2370,41 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>103018</v>
+        <v>2180</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Svartvit flugsnappare</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Ficedula hypoleuca</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Pallas, 1764)</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>par i lämplig häckbiotop</t>
-        </is>
-      </c>
+          <t>(Hedw.) Ångstr.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
           <t>Stora Saltvik, Stora Saltvik, Sm</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>590744</v>
+        <v>590681</v>
       </c>
       <c r="R18" t="n">
-        <v>6353445</v>
+        <v>6353540</v>
       </c>
       <c r="S18" t="n">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2460,10 +2460,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>125264768</v>
+        <v>125265456</v>
       </c>
       <c r="B19" t="n">
-        <v>57995</v>
+        <v>95705</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2472,25 +2472,25 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>103018</v>
+        <v>2180</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Svartvit flugsnappare</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Ficedula hypoleuca</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Pallas, 1764)</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2500,13 +2500,13 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>590735</v>
+        <v>590690</v>
       </c>
       <c r="R19" t="n">
-        <v>6353466</v>
+        <v>6353521</v>
       </c>
       <c r="S19" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>

--- a/artfynd/A 19260-2025 artfynd.xlsx
+++ b/artfynd/A 19260-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY26"/>
+  <dimension ref="A1:AY35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>125265047</v>
+        <v>125267966</v>
       </c>
       <c r="B2" t="n">
-        <v>57529</v>
+        <v>57761</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,34 +691,43 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100049</v>
+        <v>103012</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Grönsångare</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Phylloscopus sibilatrix</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
+          <t>(Bechstein, 1793)</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Stora Saltvik, Stora Saltvik, Sm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>590693</v>
+        <v>590812</v>
       </c>
       <c r="R2" t="n">
-        <v>6353472</v>
+        <v>6353560</v>
       </c>
       <c r="S2" t="n">
         <v>20</v>
@@ -753,11 +762,6 @@
           <t>2025-05-20</t>
         </is>
       </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Födosökshack</t>
-        </is>
-      </c>
       <c r="AD2" t="b">
         <v>0</v>
       </c>
@@ -770,19 +774,19 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>125265546</v>
+        <v>125267976</v>
       </c>
       <c r="B3" t="n">
         <v>95705</v>
@@ -822,13 +826,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>590707</v>
+        <v>590840</v>
       </c>
       <c r="R3" t="n">
-        <v>6353533</v>
+        <v>6353566</v>
       </c>
       <c r="S3" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -872,22 +876,22 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>125267873</v>
+        <v>125265456</v>
       </c>
       <c r="B4" t="n">
-        <v>91032</v>
+        <v>95705</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -896,25 +900,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5442</v>
+        <v>2180</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -924,13 +928,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>590814</v>
+        <v>590690</v>
       </c>
       <c r="R4" t="n">
-        <v>6353563</v>
+        <v>6353521</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -974,19 +978,19 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>125266788</v>
+        <v>125265040</v>
       </c>
       <c r="B5" t="n">
         <v>95705</v>
@@ -1026,10 +1030,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>590574</v>
+        <v>590703</v>
       </c>
       <c r="R5" t="n">
-        <v>6353534</v>
+        <v>6353508</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1088,10 +1092,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>125265888</v>
+        <v>125267309</v>
       </c>
       <c r="B6" t="n">
-        <v>57529</v>
+        <v>57995</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1104,37 +1108,46 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100049</v>
+        <v>103018</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Svartvit flugsnappare</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Ficedula hypoleuca</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
+          <t>(Pallas, 1764)</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Stora Saltvik, Stora Saltvik, Sm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>590717</v>
+        <v>590681</v>
       </c>
       <c r="R6" t="n">
-        <v>6353617</v>
+        <v>6353540</v>
       </c>
       <c r="S6" t="n">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1164,11 +1177,6 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-05-20</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Födosökshack</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1183,22 +1191,22 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>125265581</v>
+        <v>125264864</v>
       </c>
       <c r="B7" t="n">
-        <v>95705</v>
+        <v>57995</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1207,41 +1215,50 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>2180</v>
+        <v>103018</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Svartvit flugsnappare</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Ficedula hypoleuca</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
+          <t>(Pallas, 1764)</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>par i lämplig häckbiotop</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Stora Saltvik, Stora Saltvik, Sm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>590620</v>
+        <v>590744</v>
       </c>
       <c r="R7" t="n">
-        <v>6353512</v>
+        <v>6353445</v>
       </c>
       <c r="S7" t="n">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1297,10 +1314,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>125268245</v>
+        <v>125267890</v>
       </c>
       <c r="B8" t="n">
-        <v>57761</v>
+        <v>57529</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1313,37 +1330,46 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>103012</v>
+        <v>100049</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Grönsångare</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Phylloscopus sibilatrix</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Bechstein, 1793)</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Lerbro, Lerbro, Sm</t>
+          <t>Stora Saltvik, Stora Saltvik, Sm</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>590069</v>
+        <v>590812</v>
       </c>
       <c r="R8" t="n">
-        <v>6353421</v>
+        <v>6353560</v>
       </c>
       <c r="S8" t="n">
-        <v>25</v>
+        <v>40</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1387,22 +1413,22 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>125265536</v>
+        <v>125265047</v>
       </c>
       <c r="B9" t="n">
-        <v>56856</v>
+        <v>57529</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1411,20 +1437,20 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100065</v>
+        <v>100049</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Trana</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Grus grus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -1432,29 +1458,20 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
+      <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Stora Saltvik, Stora Saltvik, Sm</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>590703</v>
+        <v>590693</v>
       </c>
       <c r="R9" t="n">
-        <v>6353508</v>
+        <v>6353472</v>
       </c>
       <c r="S9" t="n">
-        <v>50</v>
+        <v>20</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1484,6 +1501,11 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-05-20</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Födosökshack</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1498,22 +1520,22 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>125265482</v>
+        <v>125265581</v>
       </c>
       <c r="B10" t="n">
-        <v>57995</v>
+        <v>95705</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1522,50 +1544,41 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>103018</v>
+        <v>2180</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Svartvit flugsnappare</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Ficedula hypoleuca</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Pallas, 1764)</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
+          <t>(Hedw.) Ångstr.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Stora Saltvik, Saltvik, Sm</t>
+          <t>Stora Saltvik, Stora Saltvik, Sm</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>590703</v>
+        <v>590620</v>
       </c>
       <c r="R10" t="n">
-        <v>6353508</v>
+        <v>6353512</v>
       </c>
       <c r="S10" t="n">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1621,10 +1634,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>125264931</v>
+        <v>125266422</v>
       </c>
       <c r="B11" t="n">
-        <v>95423</v>
+        <v>95705</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1637,21 +1650,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>2671</v>
+        <v>2180</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Fällmossa</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Antitrichia curtipendula</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Hedw.) Brid.</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1661,13 +1674,13 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>590731</v>
+        <v>590574</v>
       </c>
       <c r="R11" t="n">
-        <v>6353465</v>
+        <v>6353534</v>
       </c>
       <c r="S11" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1711,22 +1724,22 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>125267309</v>
+        <v>125267219</v>
       </c>
       <c r="B12" t="n">
-        <v>57995</v>
+        <v>95705</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1735,37 +1748,28 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>103018</v>
+        <v>2180</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Svartvit flugsnappare</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Ficedula hypoleuca</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Pallas, 1764)</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
+          <t>(Hedw.) Ångstr.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
           <t>Stora Saltvik, Stora Saltvik, Sm</t>
@@ -1778,7 +1782,7 @@
         <v>6353540</v>
       </c>
       <c r="S12" t="n">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1834,10 +1838,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>125265231</v>
+        <v>125264931</v>
       </c>
       <c r="B13" t="n">
-        <v>95705</v>
+        <v>95423</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1850,21 +1854,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>2180</v>
+        <v>2671</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Fällmossa</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Antitrichia curtipendula</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(Hedw.) Brid.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1874,13 +1878,13 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>590703</v>
+        <v>590731</v>
       </c>
       <c r="R13" t="n">
-        <v>6353508</v>
+        <v>6353465</v>
       </c>
       <c r="S13" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1924,12 +1928,12 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
@@ -2038,10 +2042,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>125266294</v>
+        <v>125264737</v>
       </c>
       <c r="B15" t="n">
-        <v>57995</v>
+        <v>57761</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2054,42 +2058,37 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>103018</v>
+        <v>103012</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Svartvit flugsnappare</t>
+          <t>Grönsångare</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Ficedula hypoleuca</t>
+          <t>Phylloscopus sibilatrix</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Pallas, 1764)</t>
+          <t>(Bechstein, 1793)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Stora Saltvik, Stora Saltvik, Sm</t>
+          <t>Stora Saltvik, Saltvik, Sm</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>590574</v>
+        <v>590732</v>
       </c>
       <c r="R15" t="n">
-        <v>6353534</v>
+        <v>6353436</v>
       </c>
       <c r="S15" t="n">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2133,22 +2132,22 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>125264864</v>
+        <v>125265228</v>
       </c>
       <c r="B16" t="n">
-        <v>57995</v>
+        <v>79428</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2161,46 +2160,37 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>103018</v>
+        <v>6453</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Svartvit flugsnappare</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Ficedula hypoleuca</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Pallas, 1764)</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>par i lämplig häckbiotop</t>
-        </is>
-      </c>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
           <t>Stora Saltvik, Stora Saltvik, Sm</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>590744</v>
+        <v>590685</v>
       </c>
       <c r="R16" t="n">
-        <v>6353445</v>
+        <v>6353472</v>
       </c>
       <c r="S16" t="n">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2244,22 +2234,22 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>125264768</v>
+        <v>125267022</v>
       </c>
       <c r="B17" t="n">
-        <v>57995</v>
+        <v>79428</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2272,21 +2262,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>103018</v>
+        <v>6453</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Svartvit flugsnappare</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Ficedula hypoleuca</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Pallas, 1764)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2296,13 +2286,13 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>590735</v>
+        <v>590681</v>
       </c>
       <c r="R17" t="n">
-        <v>6353466</v>
+        <v>6353540</v>
       </c>
       <c r="S17" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2346,22 +2336,22 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>125267219</v>
+        <v>125268245</v>
       </c>
       <c r="B18" t="n">
-        <v>95705</v>
+        <v>57761</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2370,41 +2360,41 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>2180</v>
+        <v>103012</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Grönsångare</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Phylloscopus sibilatrix</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(Bechstein, 1793)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Stora Saltvik, Stora Saltvik, Sm</t>
+          <t>Lerbro, Lerbro, Sm</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>590681</v>
+        <v>590069</v>
       </c>
       <c r="R18" t="n">
-        <v>6353540</v>
+        <v>6353421</v>
       </c>
       <c r="S18" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2448,19 +2438,19 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>125265456</v>
+        <v>125265546</v>
       </c>
       <c r="B19" t="n">
         <v>95705</v>
@@ -2500,10 +2490,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>590690</v>
+        <v>590707</v>
       </c>
       <c r="R19" t="n">
-        <v>6353521</v>
+        <v>6353533</v>
       </c>
       <c r="S19" t="n">
         <v>15</v>
@@ -2562,10 +2552,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>125267890</v>
+        <v>125265536</v>
       </c>
       <c r="B20" t="n">
-        <v>57529</v>
+        <v>56856</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2574,20 +2564,20 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100049</v>
+        <v>100065</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Trana</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Grus grus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -2602,7 +2592,7 @@
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>födosökande</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
@@ -2611,13 +2601,13 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>590812</v>
+        <v>590703</v>
       </c>
       <c r="R20" t="n">
-        <v>6353560</v>
+        <v>6353508</v>
       </c>
       <c r="S20" t="n">
-        <v>40</v>
+        <v>50</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2673,10 +2663,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>125268075</v>
+        <v>125266294</v>
       </c>
       <c r="B21" t="n">
-        <v>57948</v>
+        <v>57995</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2689,31 +2679,27 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>102999</v>
+        <v>103018</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Björktrast</t>
+          <t>Svartvit flugsnappare</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Turdus pilaris</t>
+          <t>Ficedula hypoleuca</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Pallas, 1764)</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
       <c r="M21" t="inlineStr">
         <is>
-          <t>upprörd, varnande</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
@@ -2722,10 +2708,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>590840</v>
+        <v>590574</v>
       </c>
       <c r="R21" t="n">
-        <v>6353566</v>
+        <v>6353534</v>
       </c>
       <c r="S21" t="n">
         <v>30</v>
@@ -2784,10 +2770,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>125268044</v>
+        <v>125267873</v>
       </c>
       <c r="B22" t="n">
-        <v>95705</v>
+        <v>91032</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2796,25 +2782,25 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>2180</v>
+        <v>5442</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2824,10 +2810,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>590840</v>
+        <v>590814</v>
       </c>
       <c r="R22" t="n">
-        <v>6353566</v>
+        <v>6353563</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2886,10 +2872,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>125265228</v>
+        <v>125264768</v>
       </c>
       <c r="B23" t="n">
-        <v>79428</v>
+        <v>57995</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2902,21 +2888,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6453</v>
+        <v>103018</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Svartvit flugsnappare</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Ficedula hypoleuca</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Pallas, 1764)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2926,13 +2912,13 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>590685</v>
+        <v>590735</v>
       </c>
       <c r="R23" t="n">
-        <v>6353472</v>
+        <v>6353466</v>
       </c>
       <c r="S23" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -2988,10 +2974,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>125267966</v>
+        <v>125268075</v>
       </c>
       <c r="B24" t="n">
-        <v>57761</v>
+        <v>57948</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3004,21 +2990,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>103012</v>
+        <v>102999</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Grönsångare</t>
+          <t>Björktrast</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Phylloscopus sibilatrix</t>
+          <t>Turdus pilaris</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Bechstein, 1793)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
@@ -3028,7 +3014,7 @@
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>upprörd, varnande</t>
         </is>
       </c>
       <c r="P24" t="inlineStr">
@@ -3037,13 +3023,13 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>590812</v>
+        <v>590840</v>
       </c>
       <c r="R24" t="n">
-        <v>6353560</v>
+        <v>6353566</v>
       </c>
       <c r="S24" t="n">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3099,10 +3085,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>125267022</v>
+        <v>125265888</v>
       </c>
       <c r="B25" t="n">
-        <v>79428</v>
+        <v>57529</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3115,21 +3101,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6453</v>
+        <v>100049</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3139,13 +3125,13 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>590681</v>
+        <v>590717</v>
       </c>
       <c r="R25" t="n">
-        <v>6353540</v>
+        <v>6353617</v>
       </c>
       <c r="S25" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3175,6 +3161,11 @@
       <c r="AA25" t="inlineStr">
         <is>
           <t>2025-05-20</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>Födosökshack</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3189,22 +3180,22 @@
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>125264737</v>
+        <v>125265482</v>
       </c>
       <c r="B26" t="n">
-        <v>57761</v>
+        <v>57995</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3217,37 +3208,46 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>103012</v>
+        <v>103018</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Grönsångare</t>
+          <t>Svartvit flugsnappare</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Phylloscopus sibilatrix</t>
+          <t>Ficedula hypoleuca</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Bechstein, 1793)</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr"/>
+          <t>(Pallas, 1764)</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="P26" t="inlineStr">
         <is>
           <t>Stora Saltvik, Saltvik, Sm</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>590732</v>
+        <v>590703</v>
       </c>
       <c r="R26" t="n">
-        <v>6353436</v>
+        <v>6353508</v>
       </c>
       <c r="S26" t="n">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3291,15 +3291,983 @@
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>125494689</v>
+      </c>
+      <c r="B27" t="n">
+        <v>57761</v>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>103012</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Grönsångare</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Phylloscopus sibilatrix</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>(Bechstein, 1793)</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>Stora Saltvik, Stora Saltvik, Sm</t>
+        </is>
+      </c>
+      <c r="Q27" t="n">
+        <v>590606</v>
+      </c>
+      <c r="R27" t="n">
+        <v>6353535</v>
+      </c>
+      <c r="S27" t="n">
+        <v>40</v>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>Oskarshamn</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>Döderhult</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>2025-05-29</t>
+        </is>
+      </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>2025-05-29</t>
+        </is>
+      </c>
+      <c r="AD27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT27" t="inlineStr"/>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>Jan Brenander</t>
+        </is>
+      </c>
+      <c r="AX27" t="inlineStr">
+        <is>
+          <t>Jan Brenander</t>
+        </is>
+      </c>
+      <c r="AY27" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>125494564</v>
+      </c>
+      <c r="B28" t="n">
+        <v>95705</v>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>2180</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Blåmossa</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Leucobryum glaucum</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>(Hedw.) Ångstr.</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>Stora Saltvik, Stora Saltvik, Sm</t>
+        </is>
+      </c>
+      <c r="Q28" t="n">
+        <v>590606</v>
+      </c>
+      <c r="R28" t="n">
+        <v>6353535</v>
+      </c>
+      <c r="S28" t="n">
+        <v>10</v>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>Oskarshamn</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>Döderhult</t>
+        </is>
+      </c>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>2025-05-29</t>
+        </is>
+      </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>2025-05-29</t>
+        </is>
+      </c>
+      <c r="AD28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT28" t="inlineStr"/>
+      <c r="AW28" t="inlineStr">
+        <is>
+          <t>Jan Brenander</t>
+        </is>
+      </c>
+      <c r="AX28" t="inlineStr">
+        <is>
+          <t>Jan Brenander</t>
+        </is>
+      </c>
+      <c r="AY28" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>125494799</v>
+      </c>
+      <c r="B29" t="n">
+        <v>58272</v>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>103042</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Grönfink</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Chloris chloris</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>Stora Saltvik, Stora Saltvik, Sm</t>
+        </is>
+      </c>
+      <c r="Q29" t="n">
+        <v>590514</v>
+      </c>
+      <c r="R29" t="n">
+        <v>6353595</v>
+      </c>
+      <c r="S29" t="n">
+        <v>30</v>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>Oskarshamn</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W29" t="inlineStr">
+        <is>
+          <t>Döderhult</t>
+        </is>
+      </c>
+      <c r="Y29" t="inlineStr">
+        <is>
+          <t>2025-05-29</t>
+        </is>
+      </c>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>2025-05-29</t>
+        </is>
+      </c>
+      <c r="AD29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT29" t="inlineStr"/>
+      <c r="AW29" t="inlineStr">
+        <is>
+          <t>Jan Brenander</t>
+        </is>
+      </c>
+      <c r="AX29" t="inlineStr">
+        <is>
+          <t>Jan Brenander</t>
+        </is>
+      </c>
+      <c r="AY29" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>125495192</v>
+      </c>
+      <c r="B30" t="n">
+        <v>57914</v>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>103012</v>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Grönsångare</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Phylloscopus sibilatrix</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>(Bechstein, 1793)</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>Skogstorpet  Lilla Saltvik, Skogstorpet  Lilla Saltvik, Sm</t>
+        </is>
+      </c>
+      <c r="Q30" t="n">
+        <v>590493</v>
+      </c>
+      <c r="R30" t="n">
+        <v>6353535</v>
+      </c>
+      <c r="S30" t="n">
+        <v>20</v>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>Oskarshamn</t>
+        </is>
+      </c>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W30" t="inlineStr">
+        <is>
+          <t>Döderhult</t>
+        </is>
+      </c>
+      <c r="Y30" t="inlineStr">
+        <is>
+          <t>2025-05-29</t>
+        </is>
+      </c>
+      <c r="AA30" t="inlineStr">
+        <is>
+          <t>2025-05-29</t>
+        </is>
+      </c>
+      <c r="AD30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT30" t="inlineStr"/>
+      <c r="AW30" t="inlineStr">
+        <is>
+          <t>Jan Brenander</t>
+        </is>
+      </c>
+      <c r="AX30" t="inlineStr">
+        <is>
+          <t>Jan Brenander</t>
+        </is>
+      </c>
+      <c r="AY30" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>125494786</v>
+      </c>
+      <c r="B31" t="n">
+        <v>57914</v>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>103012</v>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Grönsångare</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Phylloscopus sibilatrix</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>(Bechstein, 1793)</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>Stora Saltvik, Stora Saltvik, Sm</t>
+        </is>
+      </c>
+      <c r="Q31" t="n">
+        <v>590523</v>
+      </c>
+      <c r="R31" t="n">
+        <v>6353580</v>
+      </c>
+      <c r="S31" t="n">
+        <v>30</v>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>Oskarshamn</t>
+        </is>
+      </c>
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W31" t="inlineStr">
+        <is>
+          <t>Döderhult</t>
+        </is>
+      </c>
+      <c r="Y31" t="inlineStr">
+        <is>
+          <t>2025-05-29</t>
+        </is>
+      </c>
+      <c r="AA31" t="inlineStr">
+        <is>
+          <t>2025-05-29</t>
+        </is>
+      </c>
+      <c r="AD31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT31" t="inlineStr"/>
+      <c r="AW31" t="inlineStr">
+        <is>
+          <t>Jan Brenander</t>
+        </is>
+      </c>
+      <c r="AX31" t="inlineStr">
+        <is>
+          <t>Jan Brenander</t>
+        </is>
+      </c>
+      <c r="AY31" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>125495258</v>
+      </c>
+      <c r="B32" t="n">
+        <v>95873</v>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E32" t="n">
+        <v>2180</v>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Blåmossa</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>Leucobryum glaucum</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>(Hedw.) Ångstr.</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>Skogstorpet  Lilla Saltvik, Skogstorpet  Lilla Saltvik, Sm</t>
+        </is>
+      </c>
+      <c r="Q32" t="n">
+        <v>590493</v>
+      </c>
+      <c r="R32" t="n">
+        <v>6353535</v>
+      </c>
+      <c r="S32" t="n">
+        <v>10</v>
+      </c>
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>Oskarshamn</t>
+        </is>
+      </c>
+      <c r="V32" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W32" t="inlineStr">
+        <is>
+          <t>Döderhult</t>
+        </is>
+      </c>
+      <c r="Y32" t="inlineStr">
+        <is>
+          <t>2025-05-29</t>
+        </is>
+      </c>
+      <c r="AA32" t="inlineStr">
+        <is>
+          <t>2025-05-29</t>
+        </is>
+      </c>
+      <c r="AD32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT32" t="inlineStr"/>
+      <c r="AW32" t="inlineStr">
+        <is>
+          <t>Jan Brenander</t>
+        </is>
+      </c>
+      <c r="AX32" t="inlineStr">
+        <is>
+          <t>Jan Brenander</t>
+        </is>
+      </c>
+      <c r="AY32" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>125494037</v>
+      </c>
+      <c r="B33" t="n">
+        <v>57761</v>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E33" t="n">
+        <v>103012</v>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Grönsångare</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>Phylloscopus sibilatrix</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>(Bechstein, 1793)</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>Stora Saltvik, Stora Saltvik, Sm</t>
+        </is>
+      </c>
+      <c r="Q33" t="n">
+        <v>590499</v>
+      </c>
+      <c r="R33" t="n">
+        <v>6353442</v>
+      </c>
+      <c r="S33" t="n">
+        <v>30</v>
+      </c>
+      <c r="T33" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U33" t="inlineStr">
+        <is>
+          <t>Oskarshamn</t>
+        </is>
+      </c>
+      <c r="V33" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W33" t="inlineStr">
+        <is>
+          <t>Döderhult</t>
+        </is>
+      </c>
+      <c r="Y33" t="inlineStr">
+        <is>
+          <t>2025-05-29</t>
+        </is>
+      </c>
+      <c r="AA33" t="inlineStr">
+        <is>
+          <t>2025-05-29</t>
+        </is>
+      </c>
+      <c r="AD33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT33" t="inlineStr"/>
+      <c r="AW33" t="inlineStr">
+        <is>
+          <t>Jan Brenander</t>
+        </is>
+      </c>
+      <c r="AX33" t="inlineStr">
+        <is>
+          <t>Jan Brenander</t>
+        </is>
+      </c>
+      <c r="AY33" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>125495143</v>
+      </c>
+      <c r="B34" t="n">
+        <v>95873</v>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E34" t="n">
+        <v>2180</v>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Blåmossa</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>Leucobryum glaucum</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>(Hedw.) Ångstr.</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr"/>
+      <c r="P34" t="inlineStr">
+        <is>
+          <t>Skogstorpet  Lilla Saltvik, Skogstorpet  Lilla Saltvik, Sm</t>
+        </is>
+      </c>
+      <c r="Q34" t="n">
+        <v>590497</v>
+      </c>
+      <c r="R34" t="n">
+        <v>6353564</v>
+      </c>
+      <c r="S34" t="n">
+        <v>10</v>
+      </c>
+      <c r="T34" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U34" t="inlineStr">
+        <is>
+          <t>Oskarshamn</t>
+        </is>
+      </c>
+      <c r="V34" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W34" t="inlineStr">
+        <is>
+          <t>Döderhult</t>
+        </is>
+      </c>
+      <c r="Y34" t="inlineStr">
+        <is>
+          <t>2025-05-29</t>
+        </is>
+      </c>
+      <c r="AA34" t="inlineStr">
+        <is>
+          <t>2025-05-29</t>
+        </is>
+      </c>
+      <c r="AD34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT34" t="inlineStr"/>
+      <c r="AW34" t="inlineStr">
+        <is>
+          <t>Jan Brenander</t>
+        </is>
+      </c>
+      <c r="AX34" t="inlineStr">
+        <is>
+          <t>Jan Brenander</t>
+        </is>
+      </c>
+      <c r="AY34" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>125494897</v>
+      </c>
+      <c r="B35" t="n">
+        <v>57632</v>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E35" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="P35" t="inlineStr">
+        <is>
+          <t>Skogstorpet  Lilla Saltvik, Saltvik, Sm</t>
+        </is>
+      </c>
+      <c r="Q35" t="n">
+        <v>590484</v>
+      </c>
+      <c r="R35" t="n">
+        <v>6353599</v>
+      </c>
+      <c r="S35" t="n">
+        <v>40</v>
+      </c>
+      <c r="T35" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U35" t="inlineStr">
+        <is>
+          <t>Oskarshamn</t>
+        </is>
+      </c>
+      <c r="V35" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W35" t="inlineStr">
+        <is>
+          <t>Döderhult</t>
+        </is>
+      </c>
+      <c r="Y35" t="inlineStr">
+        <is>
+          <t>2025-05-29</t>
+        </is>
+      </c>
+      <c r="AA35" t="inlineStr">
+        <is>
+          <t>2025-05-29</t>
+        </is>
+      </c>
+      <c r="AD35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT35" t="inlineStr"/>
+      <c r="AW35" t="inlineStr">
+        <is>
+          <t>Jan Brenander</t>
+        </is>
+      </c>
+      <c r="AX35" t="inlineStr">
+        <is>
+          <t>Jan Brenander</t>
+        </is>
+      </c>
+      <c r="AY35" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 19260-2025 artfynd.xlsx
+++ b/artfynd/A 19260-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>125267966</v>
+        <v>125267219</v>
       </c>
       <c r="B2" t="n">
-        <v>57761</v>
+        <v>95873</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,50 +687,41 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>103012</v>
+        <v>2180</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Grönsångare</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Phylloscopus sibilatrix</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Bechstein, 1793)</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
+          <t>(Hedw.) Ångstr.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Stora Saltvik, Stora Saltvik, Sm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>590812</v>
+        <v>590681</v>
       </c>
       <c r="R2" t="n">
-        <v>6353560</v>
+        <v>6353540</v>
       </c>
       <c r="S2" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -786,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>125267976</v>
+        <v>125264768</v>
       </c>
       <c r="B3" t="n">
-        <v>95705</v>
+        <v>58111</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -798,25 +789,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>2180</v>
+        <v>103018</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Svartvit flugsnappare</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Ficedula hypoleuca</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(Pallas, 1764)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -826,13 +817,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>590840</v>
+        <v>590735</v>
       </c>
       <c r="R3" t="n">
-        <v>6353566</v>
+        <v>6353466</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -876,22 +867,22 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>125265456</v>
+        <v>125265546</v>
       </c>
       <c r="B4" t="n">
-        <v>95705</v>
+        <v>95873</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -928,10 +919,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>590690</v>
+        <v>590707</v>
       </c>
       <c r="R4" t="n">
-        <v>6353521</v>
+        <v>6353533</v>
       </c>
       <c r="S4" t="n">
         <v>15</v>
@@ -990,10 +981,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>125265040</v>
+        <v>125266788</v>
       </c>
       <c r="B5" t="n">
-        <v>95705</v>
+        <v>95873</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1030,10 +1021,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>590703</v>
+        <v>590574</v>
       </c>
       <c r="R5" t="n">
-        <v>6353508</v>
+        <v>6353534</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1095,7 +1086,7 @@
         <v>125267309</v>
       </c>
       <c r="B6" t="n">
-        <v>57995</v>
+        <v>58111</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1203,10 +1194,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>125264864</v>
+        <v>125267966</v>
       </c>
       <c r="B7" t="n">
-        <v>57995</v>
+        <v>57914</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1219,31 +1210,31 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>103018</v>
+        <v>103012</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Svartvit flugsnappare</t>
+          <t>Grönsångare</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Ficedula hypoleuca</t>
+          <t>Phylloscopus sibilatrix</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Pallas, 1764)</t>
+          <t>(Bechstein, 1793)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>par i lämplig häckbiotop</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -1252,13 +1243,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>590744</v>
+        <v>590812</v>
       </c>
       <c r="R7" t="n">
-        <v>6353445</v>
+        <v>6353560</v>
       </c>
       <c r="S7" t="n">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1314,10 +1305,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>125267890</v>
+        <v>125264931</v>
       </c>
       <c r="B8" t="n">
-        <v>57529</v>
+        <v>95591</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1326,50 +1317,41 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100049</v>
+        <v>2671</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Fällmossa</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Antitrichia curtipendula</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
+          <t>(Hedw.) Brid.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Stora Saltvik, Stora Saltvik, Sm</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>590812</v>
+        <v>590731</v>
       </c>
       <c r="R8" t="n">
-        <v>6353560</v>
+        <v>6353465</v>
       </c>
       <c r="S8" t="n">
-        <v>40</v>
+        <v>15</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1413,22 +1395,22 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>125265047</v>
+        <v>125265581</v>
       </c>
       <c r="B9" t="n">
-        <v>57529</v>
+        <v>95873</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1437,25 +1419,25 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100049</v>
+        <v>2180</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1465,13 +1447,13 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>590693</v>
+        <v>590620</v>
       </c>
       <c r="R9" t="n">
-        <v>6353472</v>
+        <v>6353512</v>
       </c>
       <c r="S9" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1501,11 +1483,6 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-05-20</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Födosökshack</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1520,22 +1497,22 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>125265581</v>
+        <v>125268245</v>
       </c>
       <c r="B10" t="n">
-        <v>95705</v>
+        <v>57914</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1544,41 +1521,41 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>2180</v>
+        <v>103012</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Grönsångare</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Phylloscopus sibilatrix</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(Bechstein, 1793)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Stora Saltvik, Stora Saltvik, Sm</t>
+          <t>Lerbro, Lerbro, Sm</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>590620</v>
+        <v>590069</v>
       </c>
       <c r="R10" t="n">
-        <v>6353512</v>
+        <v>6353421</v>
       </c>
       <c r="S10" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1622,22 +1599,22 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>125266422</v>
+        <v>125266294</v>
       </c>
       <c r="B11" t="n">
-        <v>95705</v>
+        <v>58111</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1646,28 +1623,33 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>2180</v>
+        <v>103018</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Svartvit flugsnappare</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Ficedula hypoleuca</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(Pallas, 1764)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Stora Saltvik, Stora Saltvik, Sm</t>
@@ -1680,7 +1662,7 @@
         <v>6353534</v>
       </c>
       <c r="S11" t="n">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1736,10 +1718,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>125267219</v>
+        <v>125265888</v>
       </c>
       <c r="B12" t="n">
-        <v>95705</v>
+        <v>57632</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1748,25 +1730,25 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>2180</v>
+        <v>100049</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1776,13 +1758,13 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>590681</v>
+        <v>590717</v>
       </c>
       <c r="R12" t="n">
-        <v>6353540</v>
+        <v>6353617</v>
       </c>
       <c r="S12" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1812,6 +1794,11 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-05-20</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Födosökshack</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1826,22 +1813,22 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>125264931</v>
+        <v>125267022</v>
       </c>
       <c r="B13" t="n">
-        <v>95423</v>
+        <v>79565</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1850,25 +1837,25 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>2671</v>
+        <v>6453</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Fällmossa</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Antitrichia curtipendula</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Hedw.) Brid.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1878,13 +1865,13 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>590731</v>
+        <v>590681</v>
       </c>
       <c r="R13" t="n">
-        <v>6353465</v>
+        <v>6353540</v>
       </c>
       <c r="S13" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1928,22 +1915,22 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>125265667</v>
+        <v>125264737</v>
       </c>
       <c r="B14" t="n">
-        <v>95705</v>
+        <v>57914</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1952,41 +1939,41 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>2180</v>
+        <v>103012</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Grönsångare</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Phylloscopus sibilatrix</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(Bechstein, 1793)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Stora Saltvik, Stora Saltvik, Sm</t>
+          <t>Stora Saltvik, Saltvik, Sm</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>590705</v>
+        <v>590732</v>
       </c>
       <c r="R14" t="n">
-        <v>6353579</v>
+        <v>6353436</v>
       </c>
       <c r="S14" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2042,10 +2029,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>125264737</v>
+        <v>125265536</v>
       </c>
       <c r="B15" t="n">
-        <v>57761</v>
+        <v>56949</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2054,41 +2041,50 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>103012</v>
+        <v>100065</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Grönsångare</t>
+          <t>Trana</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Phylloscopus sibilatrix</t>
+          <t>Grus grus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Bechstein, 1793)</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Stora Saltvik, Saltvik, Sm</t>
+          <t>Stora Saltvik, Stora Saltvik, Sm</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>590732</v>
+        <v>590703</v>
       </c>
       <c r="R15" t="n">
-        <v>6353436</v>
+        <v>6353508</v>
       </c>
       <c r="S15" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2132,22 +2128,22 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>125265228</v>
+        <v>125267890</v>
       </c>
       <c r="B16" t="n">
-        <v>79428</v>
+        <v>57632</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2160,37 +2156,46 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6453</v>
+        <v>100049</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="P16" t="inlineStr">
         <is>
           <t>Stora Saltvik, Stora Saltvik, Sm</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>590685</v>
+        <v>590812</v>
       </c>
       <c r="R16" t="n">
-        <v>6353472</v>
+        <v>6353560</v>
       </c>
       <c r="S16" t="n">
-        <v>10</v>
+        <v>40</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2234,22 +2239,22 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>125267022</v>
+        <v>125268075</v>
       </c>
       <c r="B17" t="n">
-        <v>79428</v>
+        <v>58065</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2262,37 +2267,46 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6453</v>
+        <v>102999</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Björktrast</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Turdus pilaris</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
       <c r="P17" t="inlineStr">
         <is>
           <t>Stora Saltvik, Stora Saltvik, Sm</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>590681</v>
+        <v>590840</v>
       </c>
       <c r="R17" t="n">
-        <v>6353540</v>
+        <v>6353566</v>
       </c>
       <c r="S17" t="n">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2348,10 +2362,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>125268245</v>
+        <v>125265228</v>
       </c>
       <c r="B18" t="n">
-        <v>57761</v>
+        <v>79565</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2364,37 +2378,37 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>103012</v>
+        <v>6453</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Grönsångare</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Phylloscopus sibilatrix</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Bechstein, 1793)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Lerbro, Lerbro, Sm</t>
+          <t>Stora Saltvik, Stora Saltvik, Sm</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>590069</v>
+        <v>590685</v>
       </c>
       <c r="R18" t="n">
-        <v>6353421</v>
+        <v>6353472</v>
       </c>
       <c r="S18" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2450,10 +2464,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>125265546</v>
+        <v>125268044</v>
       </c>
       <c r="B19" t="n">
-        <v>95705</v>
+        <v>95873</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2490,13 +2504,13 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>590707</v>
+        <v>590840</v>
       </c>
       <c r="R19" t="n">
-        <v>6353533</v>
+        <v>6353566</v>
       </c>
       <c r="S19" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2540,22 +2554,22 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>125265536</v>
+        <v>125265231</v>
       </c>
       <c r="B20" t="n">
-        <v>56856</v>
+        <v>95873</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2568,33 +2582,24 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100065</v>
+        <v>2180</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Trana</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Grus grus</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
+          <t>(Hedw.) Ångstr.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
           <t>Stora Saltvik, Stora Saltvik, Sm</t>
@@ -2607,7 +2612,7 @@
         <v>6353508</v>
       </c>
       <c r="S20" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2663,10 +2668,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>125266294</v>
+        <v>125267873</v>
       </c>
       <c r="B21" t="n">
-        <v>57995</v>
+        <v>91186</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2679,42 +2684,37 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>103018</v>
+        <v>5442</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Svartvit flugsnappare</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Ficedula hypoleuca</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Pallas, 1764)</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
       <c r="P21" t="inlineStr">
         <is>
           <t>Stora Saltvik, Stora Saltvik, Sm</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>590574</v>
+        <v>590814</v>
       </c>
       <c r="R21" t="n">
-        <v>6353534</v>
+        <v>6353563</v>
       </c>
       <c r="S21" t="n">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2770,10 +2770,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>125267873</v>
+        <v>125265667</v>
       </c>
       <c r="B22" t="n">
-        <v>91032</v>
+        <v>95873</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2782,25 +2782,25 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>5442</v>
+        <v>2180</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2810,10 +2810,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>590814</v>
+        <v>590705</v>
       </c>
       <c r="R22" t="n">
-        <v>6353563</v>
+        <v>6353579</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2860,22 +2860,22 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>125264768</v>
+        <v>125264864</v>
       </c>
       <c r="B23" t="n">
-        <v>57995</v>
+        <v>58111</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2905,20 +2905,29 @@
           <t>(Pallas, 1764)</t>
         </is>
       </c>
-      <c r="I23" t="inlineStr"/>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>par i lämplig häckbiotop</t>
+        </is>
+      </c>
       <c r="P23" t="inlineStr">
         <is>
           <t>Stora Saltvik, Stora Saltvik, Sm</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>590735</v>
+        <v>590744</v>
       </c>
       <c r="R23" t="n">
-        <v>6353466</v>
+        <v>6353445</v>
       </c>
       <c r="S23" t="n">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -2962,22 +2971,22 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>125268075</v>
+        <v>125265047</v>
       </c>
       <c r="B24" t="n">
-        <v>57948</v>
+        <v>57632</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -2990,46 +2999,37 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>102999</v>
+        <v>100049</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Björktrast</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Turdus pilaris</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M24" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
           <t>Stora Saltvik, Stora Saltvik, Sm</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>590840</v>
+        <v>590693</v>
       </c>
       <c r="R24" t="n">
-        <v>6353566</v>
+        <v>6353472</v>
       </c>
       <c r="S24" t="n">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3059,6 +3059,11 @@
       <c r="AA24" t="inlineStr">
         <is>
           <t>2025-05-20</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>Födosökshack</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3073,22 +3078,22 @@
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>125265888</v>
+        <v>125265456</v>
       </c>
       <c r="B25" t="n">
-        <v>57529</v>
+        <v>95873</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3097,25 +3102,25 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>100049</v>
+        <v>2180</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3125,13 +3130,13 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>590717</v>
+        <v>590690</v>
       </c>
       <c r="R25" t="n">
-        <v>6353617</v>
+        <v>6353521</v>
       </c>
       <c r="S25" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3161,11 +3166,6 @@
       <c r="AA25" t="inlineStr">
         <is>
           <t>2025-05-20</t>
-        </is>
-      </c>
-      <c r="AC25" t="inlineStr">
-        <is>
-          <t>Födosökshack</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3195,7 +3195,7 @@
         <v>125265482</v>
       </c>
       <c r="B26" t="n">
-        <v>57995</v>
+        <v>58111</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3303,10 +3303,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>125494689</v>
+        <v>125495143</v>
       </c>
       <c r="B27" t="n">
-        <v>57761</v>
+        <v>95873</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3315,50 +3315,41 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>103012</v>
+        <v>2180</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Grönsångare</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Phylloscopus sibilatrix</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Bechstein, 1793)</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M27" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
+          <t>(Hedw.) Ångstr.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Stora Saltvik, Stora Saltvik, Sm</t>
+          <t>Skogstorpet  Lilla Saltvik, Skogstorpet  Lilla Saltvik, Sm</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>590606</v>
+        <v>590497</v>
       </c>
       <c r="R27" t="n">
-        <v>6353535</v>
+        <v>6353564</v>
       </c>
       <c r="S27" t="n">
-        <v>40</v>
+        <v>10</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3414,10 +3405,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>125494564</v>
+        <v>125494689</v>
       </c>
       <c r="B28" t="n">
-        <v>95705</v>
+        <v>57914</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3426,28 +3417,37 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>2180</v>
+        <v>103012</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Grönsångare</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Phylloscopus sibilatrix</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr"/>
+          <t>(Bechstein, 1793)</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="P28" t="inlineStr">
         <is>
           <t>Stora Saltvik, Stora Saltvik, Sm</t>
@@ -3460,7 +3460,7 @@
         <v>6353535</v>
       </c>
       <c r="S28" t="n">
-        <v>10</v>
+        <v>40</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3516,10 +3516,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>125494799</v>
+        <v>125495192</v>
       </c>
       <c r="B29" t="n">
-        <v>58272</v>
+        <v>57914</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3528,25 +3528,25 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>103042</v>
+        <v>103012</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Grönfink</t>
+          <t>Grönsångare</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Chloris chloris</t>
+          <t>Phylloscopus sibilatrix</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Bechstein, 1793)</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
@@ -3561,17 +3561,17 @@
       </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Stora Saltvik, Stora Saltvik, Sm</t>
+          <t>Skogstorpet  Lilla Saltvik, Skogstorpet  Lilla Saltvik, Sm</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>590514</v>
+        <v>590493</v>
       </c>
       <c r="R29" t="n">
-        <v>6353595</v>
+        <v>6353535</v>
       </c>
       <c r="S29" t="n">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3627,10 +3627,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>125495192</v>
+        <v>125494799</v>
       </c>
       <c r="B30" t="n">
-        <v>57914</v>
+        <v>58272</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3639,25 +3639,25 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>103012</v>
+        <v>103042</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Grönsångare</t>
+          <t>Grönfink</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Phylloscopus sibilatrix</t>
+          <t>Chloris chloris</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Bechstein, 1793)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
@@ -3672,17 +3672,17 @@
       </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Skogstorpet  Lilla Saltvik, Skogstorpet  Lilla Saltvik, Sm</t>
+          <t>Stora Saltvik, Stora Saltvik, Sm</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>590493</v>
+        <v>590514</v>
       </c>
       <c r="R30" t="n">
-        <v>6353535</v>
+        <v>6353595</v>
       </c>
       <c r="S30" t="n">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -3738,10 +3738,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>125494786</v>
+        <v>125494564</v>
       </c>
       <c r="B31" t="n">
-        <v>57914</v>
+        <v>95873</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3750,46 +3750,41 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>103012</v>
+        <v>2180</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Grönsångare</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Phylloscopus sibilatrix</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Bechstein, 1793)</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
-      <c r="M31" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
       <c r="P31" t="inlineStr">
         <is>
           <t>Stora Saltvik, Stora Saltvik, Sm</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>590523</v>
+        <v>590606</v>
       </c>
       <c r="R31" t="n">
-        <v>6353580</v>
+        <v>6353535</v>
       </c>
       <c r="S31" t="n">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -3845,10 +3840,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>125495258</v>
+        <v>125494897</v>
       </c>
       <c r="B32" t="n">
-        <v>95873</v>
+        <v>57632</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -3857,41 +3852,50 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>2180</v>
+        <v>100049</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Skogstorpet  Lilla Saltvik, Skogstorpet  Lilla Saltvik, Sm</t>
+          <t>Skogstorpet  Lilla Saltvik, Saltvik, Sm</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>590493</v>
+        <v>590484</v>
       </c>
       <c r="R32" t="n">
-        <v>6353535</v>
+        <v>6353599</v>
       </c>
       <c r="S32" t="n">
-        <v>10</v>
+        <v>40</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -3950,7 +3954,7 @@
         <v>125494037</v>
       </c>
       <c r="B33" t="n">
-        <v>57761</v>
+        <v>57914</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4058,10 +4062,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>125495143</v>
+        <v>125494786</v>
       </c>
       <c r="B34" t="n">
-        <v>95873</v>
+        <v>57914</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4070,41 +4074,46 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>2180</v>
+        <v>103012</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Grönsångare</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Phylloscopus sibilatrix</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(Bechstein, 1793)</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Skogstorpet  Lilla Saltvik, Skogstorpet  Lilla Saltvik, Sm</t>
+          <t>Stora Saltvik, Stora Saltvik, Sm</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>590497</v>
+        <v>590523</v>
       </c>
       <c r="R34" t="n">
-        <v>6353564</v>
+        <v>6353580</v>
       </c>
       <c r="S34" t="n">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4160,10 +4169,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>125494897</v>
+        <v>125495258</v>
       </c>
       <c r="B35" t="n">
-        <v>57632</v>
+        <v>95873</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4172,50 +4181,41 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>100049</v>
+        <v>2180</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M35" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
+          <t>(Hedw.) Ångstr.</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Skogstorpet  Lilla Saltvik, Saltvik, Sm</t>
+          <t>Skogstorpet  Lilla Saltvik, Skogstorpet  Lilla Saltvik, Sm</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>590484</v>
+        <v>590493</v>
       </c>
       <c r="R35" t="n">
-        <v>6353599</v>
+        <v>6353535</v>
       </c>
       <c r="S35" t="n">
-        <v>40</v>
+        <v>10</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>

--- a/artfynd/A 19260-2025 artfynd.xlsx
+++ b/artfynd/A 19260-2025 artfynd.xlsx
@@ -2362,10 +2362,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>125265228</v>
+        <v>125268044</v>
       </c>
       <c r="B18" t="n">
-        <v>79565</v>
+        <v>95873</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2374,25 +2374,25 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6453</v>
+        <v>2180</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2402,10 +2402,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>590685</v>
+        <v>590840</v>
       </c>
       <c r="R18" t="n">
-        <v>6353472</v>
+        <v>6353566</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2452,22 +2452,22 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>125268044</v>
+        <v>125265228</v>
       </c>
       <c r="B19" t="n">
-        <v>95873</v>
+        <v>79565</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2476,25 +2476,25 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>2180</v>
+        <v>6453</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2504,10 +2504,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>590840</v>
+        <v>590685</v>
       </c>
       <c r="R19" t="n">
-        <v>6353566</v>
+        <v>6353472</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2554,12 +2554,12 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>

--- a/artfynd/A 19260-2025 artfynd.xlsx
+++ b/artfynd/A 19260-2025 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>125267219</v>
+        <v>125265722</v>
       </c>
       <c r="B2" t="n">
         <v>95873</v>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>590681</v>
+        <v>590620</v>
       </c>
       <c r="R2" t="n">
-        <v>6353540</v>
+        <v>6353512</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>125264768</v>
+        <v>125265047</v>
       </c>
       <c r="B3" t="n">
-        <v>58111</v>
+        <v>57632</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,21 +793,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>103018</v>
+        <v>100049</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Svartvit flugsnappare</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Ficedula hypoleuca</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Pallas, 1764)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,13 +817,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>590735</v>
+        <v>590693</v>
       </c>
       <c r="R3" t="n">
-        <v>6353466</v>
+        <v>6353472</v>
       </c>
       <c r="S3" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -853,6 +853,11 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-05-20</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Födosökshack</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -879,10 +884,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>125265546</v>
+        <v>125266294</v>
       </c>
       <c r="B4" t="n">
-        <v>95873</v>
+        <v>58111</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -891,41 +896,46 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>2180</v>
+        <v>103018</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Svartvit flugsnappare</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Ficedula hypoleuca</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(Pallas, 1764)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Stora Saltvik, Stora Saltvik, Sm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>590707</v>
+        <v>590574</v>
       </c>
       <c r="R4" t="n">
-        <v>6353533</v>
+        <v>6353534</v>
       </c>
       <c r="S4" t="n">
-        <v>15</v>
+        <v>30</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -969,22 +979,22 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>125266788</v>
+        <v>125264864</v>
       </c>
       <c r="B5" t="n">
-        <v>95873</v>
+        <v>58111</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -993,41 +1003,50 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>2180</v>
+        <v>103018</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Svartvit flugsnappare</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Ficedula hypoleuca</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
+          <t>(Pallas, 1764)</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>par i lämplig häckbiotop</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Stora Saltvik, Stora Saltvik, Sm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>590574</v>
+        <v>590744</v>
       </c>
       <c r="R5" t="n">
-        <v>6353534</v>
+        <v>6353445</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1083,10 +1102,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>125267309</v>
+        <v>125268075</v>
       </c>
       <c r="B6" t="n">
-        <v>58111</v>
+        <v>58065</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1099,21 +1118,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>103018</v>
+        <v>102999</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Svartvit flugsnappare</t>
+          <t>Björktrast</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Ficedula hypoleuca</t>
+          <t>Turdus pilaris</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Pallas, 1764)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -1123,7 +1142,7 @@
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>upprörd, varnande</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -1132,10 +1151,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>590681</v>
+        <v>590840</v>
       </c>
       <c r="R6" t="n">
-        <v>6353540</v>
+        <v>6353566</v>
       </c>
       <c r="S6" t="n">
         <v>30</v>
@@ -1194,10 +1213,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>125267966</v>
+        <v>125265228</v>
       </c>
       <c r="B7" t="n">
-        <v>57914</v>
+        <v>79565</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1210,46 +1229,37 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>103012</v>
+        <v>6453</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Grönsångare</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Phylloscopus sibilatrix</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Bechstein, 1793)</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Stora Saltvik, Stora Saltvik, Sm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>590812</v>
+        <v>590685</v>
       </c>
       <c r="R7" t="n">
-        <v>6353560</v>
+        <v>6353472</v>
       </c>
       <c r="S7" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1293,22 +1303,22 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>125264931</v>
+        <v>125265888</v>
       </c>
       <c r="B8" t="n">
-        <v>95591</v>
+        <v>57632</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1317,25 +1327,25 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>2671</v>
+        <v>100049</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Fällmossa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Antitrichia curtipendula</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Hedw.) Brid.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1345,13 +1355,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>590731</v>
+        <v>590717</v>
       </c>
       <c r="R8" t="n">
-        <v>6353465</v>
+        <v>6353617</v>
       </c>
       <c r="S8" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1381,6 +1391,11 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-05-20</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Födosökshack</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1407,10 +1422,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>125265581</v>
+        <v>125267873</v>
       </c>
       <c r="B9" t="n">
-        <v>95873</v>
+        <v>91186</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1419,25 +1434,25 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>2180</v>
+        <v>5442</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1447,10 +1462,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>590620</v>
+        <v>590814</v>
       </c>
       <c r="R9" t="n">
-        <v>6353512</v>
+        <v>6353563</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1509,10 +1524,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>125268245</v>
+        <v>125265536</v>
       </c>
       <c r="B10" t="n">
-        <v>57914</v>
+        <v>56949</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1521,41 +1536,50 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>103012</v>
+        <v>100065</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Grönsångare</t>
+          <t>Trana</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Phylloscopus sibilatrix</t>
+          <t>Grus grus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Bechstein, 1793)</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Lerbro, Lerbro, Sm</t>
+          <t>Stora Saltvik, Stora Saltvik, Sm</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>590069</v>
+        <v>590703</v>
       </c>
       <c r="R10" t="n">
-        <v>6353421</v>
+        <v>6353508</v>
       </c>
       <c r="S10" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1599,22 +1623,22 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>125266294</v>
+        <v>125266422</v>
       </c>
       <c r="B11" t="n">
-        <v>58111</v>
+        <v>95873</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1623,33 +1647,28 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>103018</v>
+        <v>2180</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Svartvit flugsnappare</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Ficedula hypoleuca</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Pallas, 1764)</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Stora Saltvik, Stora Saltvik, Sm</t>
@@ -1662,7 +1681,7 @@
         <v>6353534</v>
       </c>
       <c r="S11" t="n">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1718,10 +1737,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>125265888</v>
+        <v>125268245</v>
       </c>
       <c r="B12" t="n">
-        <v>57632</v>
+        <v>57914</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1734,37 +1753,37 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100049</v>
+        <v>103012</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Grönsångare</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Phylloscopus sibilatrix</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Bechstein, 1793)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Stora Saltvik, Stora Saltvik, Sm</t>
+          <t>Lerbro, Lerbro, Sm</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>590717</v>
+        <v>590069</v>
       </c>
       <c r="R12" t="n">
-        <v>6353617</v>
+        <v>6353421</v>
       </c>
       <c r="S12" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1794,11 +1813,6 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-05-20</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>Födosökshack</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1825,10 +1839,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>125267022</v>
+        <v>125267890</v>
       </c>
       <c r="B13" t="n">
-        <v>79565</v>
+        <v>57632</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1841,37 +1855,46 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6453</v>
+        <v>100049</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Stora Saltvik, Stora Saltvik, Sm</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>590681</v>
+        <v>590812</v>
       </c>
       <c r="R13" t="n">
-        <v>6353540</v>
+        <v>6353560</v>
       </c>
       <c r="S13" t="n">
-        <v>10</v>
+        <v>40</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1927,10 +1950,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>125264737</v>
+        <v>125264768</v>
       </c>
       <c r="B14" t="n">
-        <v>57914</v>
+        <v>58111</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1943,34 +1966,34 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>103012</v>
+        <v>103018</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Grönsångare</t>
+          <t>Svartvit flugsnappare</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Phylloscopus sibilatrix</t>
+          <t>Ficedula hypoleuca</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Bechstein, 1793)</t>
+          <t>(Pallas, 1764)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Stora Saltvik, Saltvik, Sm</t>
+          <t>Stora Saltvik, Stora Saltvik, Sm</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>590732</v>
+        <v>590735</v>
       </c>
       <c r="R14" t="n">
-        <v>6353436</v>
+        <v>6353466</v>
       </c>
       <c r="S14" t="n">
         <v>25</v>
@@ -2029,10 +2052,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>125265536</v>
+        <v>125268044</v>
       </c>
       <c r="B15" t="n">
-        <v>56949</v>
+        <v>95873</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2045,46 +2068,37 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100065</v>
+        <v>2180</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Trana</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Grus grus</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
+          <t>(Hedw.) Ångstr.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
           <t>Stora Saltvik, Stora Saltvik, Sm</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>590703</v>
+        <v>590840</v>
       </c>
       <c r="R15" t="n">
-        <v>6353508</v>
+        <v>6353566</v>
       </c>
       <c r="S15" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2140,10 +2154,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>125267890</v>
+        <v>125264931</v>
       </c>
       <c r="B16" t="n">
-        <v>57632</v>
+        <v>95591</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2152,50 +2166,41 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100049</v>
+        <v>2671</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Fällmossa</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Antitrichia curtipendula</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
+          <t>(Hedw.) Brid.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
           <t>Stora Saltvik, Stora Saltvik, Sm</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>590812</v>
+        <v>590731</v>
       </c>
       <c r="R16" t="n">
-        <v>6353560</v>
+        <v>6353465</v>
       </c>
       <c r="S16" t="n">
-        <v>40</v>
+        <v>15</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2239,22 +2244,22 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>125268075</v>
+        <v>125267219</v>
       </c>
       <c r="B17" t="n">
-        <v>58065</v>
+        <v>95873</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2263,50 +2268,41 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>102999</v>
+        <v>2180</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Björktrast</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Turdus pilaris</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
+          <t>(Hedw.) Ångstr.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
           <t>Stora Saltvik, Stora Saltvik, Sm</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>590840</v>
+        <v>590681</v>
       </c>
       <c r="R17" t="n">
-        <v>6353566</v>
+        <v>6353540</v>
       </c>
       <c r="S17" t="n">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2362,10 +2358,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>125268044</v>
+        <v>125265482</v>
       </c>
       <c r="B18" t="n">
-        <v>95873</v>
+        <v>58111</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2374,41 +2370,50 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>2180</v>
+        <v>103018</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Svartvit flugsnappare</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Ficedula hypoleuca</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr"/>
+          <t>(Pallas, 1764)</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Stora Saltvik, Stora Saltvik, Sm</t>
+          <t>Stora Saltvik, Saltvik, Sm</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>590840</v>
+        <v>590703</v>
       </c>
       <c r="R18" t="n">
-        <v>6353566</v>
+        <v>6353508</v>
       </c>
       <c r="S18" t="n">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2464,10 +2469,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>125265228</v>
+        <v>125265546</v>
       </c>
       <c r="B19" t="n">
-        <v>79565</v>
+        <v>95873</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2476,25 +2481,25 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6453</v>
+        <v>2180</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2504,13 +2509,13 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>590685</v>
+        <v>590707</v>
       </c>
       <c r="R19" t="n">
-        <v>6353472</v>
+        <v>6353533</v>
       </c>
       <c r="S19" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2566,7 +2571,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>125265231</v>
+        <v>125265456</v>
       </c>
       <c r="B20" t="n">
         <v>95873</v>
@@ -2606,13 +2611,13 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>590703</v>
+        <v>590690</v>
       </c>
       <c r="R20" t="n">
-        <v>6353508</v>
+        <v>6353521</v>
       </c>
       <c r="S20" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2656,22 +2661,22 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>125267873</v>
+        <v>125264737</v>
       </c>
       <c r="B21" t="n">
-        <v>91186</v>
+        <v>57914</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2684,37 +2689,37 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>5442</v>
+        <v>103012</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Grönsångare</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Phylloscopus sibilatrix</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Bechstein, 1793)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Stora Saltvik, Stora Saltvik, Sm</t>
+          <t>Stora Saltvik, Saltvik, Sm</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>590814</v>
+        <v>590732</v>
       </c>
       <c r="R21" t="n">
-        <v>6353563</v>
+        <v>6353436</v>
       </c>
       <c r="S21" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2758,22 +2763,22 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>125265667</v>
+        <v>125267309</v>
       </c>
       <c r="B22" t="n">
-        <v>95873</v>
+        <v>58111</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2782,41 +2787,50 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>2180</v>
+        <v>103018</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Svartvit flugsnappare</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Ficedula hypoleuca</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr"/>
+          <t>(Pallas, 1764)</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="P22" t="inlineStr">
         <is>
           <t>Stora Saltvik, Stora Saltvik, Sm</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>590705</v>
+        <v>590681</v>
       </c>
       <c r="R22" t="n">
-        <v>6353579</v>
+        <v>6353540</v>
       </c>
       <c r="S22" t="n">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -2860,22 +2874,22 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>125264864</v>
+        <v>125265231</v>
       </c>
       <c r="B23" t="n">
-        <v>58111</v>
+        <v>95873</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2884,50 +2898,41 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>103018</v>
+        <v>2180</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Svartvit flugsnappare</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Ficedula hypoleuca</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Pallas, 1764)</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>par i lämplig häckbiotop</t>
-        </is>
-      </c>
+          <t>(Hedw.) Ångstr.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
           <t>Stora Saltvik, Stora Saltvik, Sm</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>590744</v>
+        <v>590703</v>
       </c>
       <c r="R23" t="n">
-        <v>6353445</v>
+        <v>6353508</v>
       </c>
       <c r="S23" t="n">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -2983,10 +2988,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>125265047</v>
+        <v>125267966</v>
       </c>
       <c r="B24" t="n">
-        <v>57632</v>
+        <v>57914</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -2999,34 +3004,43 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>100049</v>
+        <v>103012</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Grönsångare</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Phylloscopus sibilatrix</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr"/>
+          <t>(Bechstein, 1793)</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="P24" t="inlineStr">
         <is>
           <t>Stora Saltvik, Stora Saltvik, Sm</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>590693</v>
+        <v>590812</v>
       </c>
       <c r="R24" t="n">
-        <v>6353472</v>
+        <v>6353560</v>
       </c>
       <c r="S24" t="n">
         <v>20</v>
@@ -3061,11 +3075,6 @@
           <t>2025-05-20</t>
         </is>
       </c>
-      <c r="AC24" t="inlineStr">
-        <is>
-          <t>Födosökshack</t>
-        </is>
-      </c>
       <c r="AD24" t="b">
         <v>0</v>
       </c>
@@ -3078,22 +3087,22 @@
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>125265456</v>
+        <v>125267022</v>
       </c>
       <c r="B25" t="n">
-        <v>95873</v>
+        <v>79565</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3102,25 +3111,25 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>2180</v>
+        <v>6453</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3130,13 +3139,13 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>590690</v>
+        <v>590681</v>
       </c>
       <c r="R25" t="n">
-        <v>6353521</v>
+        <v>6353540</v>
       </c>
       <c r="S25" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3180,22 +3189,22 @@
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>125265482</v>
+        <v>125265667</v>
       </c>
       <c r="B26" t="n">
-        <v>58111</v>
+        <v>95873</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3204,50 +3213,41 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>103018</v>
+        <v>2180</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Svartvit flugsnappare</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Ficedula hypoleuca</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Pallas, 1764)</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M26" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
+          <t>(Hedw.) Ångstr.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Stora Saltvik, Saltvik, Sm</t>
+          <t>Stora Saltvik, Stora Saltvik, Sm</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>590703</v>
+        <v>590705</v>
       </c>
       <c r="R26" t="n">
-        <v>6353508</v>
+        <v>6353579</v>
       </c>
       <c r="S26" t="n">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3291,22 +3291,22 @@
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>125495143</v>
+        <v>125495192</v>
       </c>
       <c r="B27" t="n">
-        <v>95873</v>
+        <v>57914</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3315,41 +3315,50 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>2180</v>
+        <v>103012</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Grönsångare</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Phylloscopus sibilatrix</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr"/>
+          <t>(Bechstein, 1793)</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="P27" t="inlineStr">
         <is>
           <t>Skogstorpet  Lilla Saltvik, Skogstorpet  Lilla Saltvik, Sm</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>590497</v>
+        <v>590493</v>
       </c>
       <c r="R27" t="n">
-        <v>6353564</v>
+        <v>6353535</v>
       </c>
       <c r="S27" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3405,10 +3414,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>125494689</v>
+        <v>125495143</v>
       </c>
       <c r="B28" t="n">
-        <v>57914</v>
+        <v>95873</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3417,50 +3426,41 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>103012</v>
+        <v>2180</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Grönsångare</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Phylloscopus sibilatrix</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Bechstein, 1793)</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M28" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
+          <t>(Hedw.) Ångstr.</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Stora Saltvik, Stora Saltvik, Sm</t>
+          <t>Skogstorpet  Lilla Saltvik, Skogstorpet  Lilla Saltvik, Sm</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>590606</v>
+        <v>590497</v>
       </c>
       <c r="R28" t="n">
-        <v>6353535</v>
+        <v>6353564</v>
       </c>
       <c r="S28" t="n">
-        <v>40</v>
+        <v>10</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3516,10 +3516,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>125495192</v>
+        <v>125494564</v>
       </c>
       <c r="B29" t="n">
-        <v>57914</v>
+        <v>95873</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3528,50 +3528,41 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>103012</v>
+        <v>2180</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Grönsångare</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Phylloscopus sibilatrix</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Bechstein, 1793)</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M29" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
+          <t>(Hedw.) Ångstr.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Skogstorpet  Lilla Saltvik, Skogstorpet  Lilla Saltvik, Sm</t>
+          <t>Stora Saltvik, Stora Saltvik, Sm</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>590493</v>
+        <v>590606</v>
       </c>
       <c r="R29" t="n">
         <v>6353535</v>
       </c>
       <c r="S29" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3627,10 +3618,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>125494799</v>
+        <v>125495258</v>
       </c>
       <c r="B30" t="n">
-        <v>58272</v>
+        <v>95873</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3639,50 +3630,41 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>103042</v>
+        <v>2180</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Grönfink</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Chloris chloris</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M30" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
+          <t>(Hedw.) Ångstr.</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Stora Saltvik, Stora Saltvik, Sm</t>
+          <t>Skogstorpet  Lilla Saltvik, Skogstorpet  Lilla Saltvik, Sm</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>590514</v>
+        <v>590493</v>
       </c>
       <c r="R30" t="n">
-        <v>6353595</v>
+        <v>6353535</v>
       </c>
       <c r="S30" t="n">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -3738,10 +3720,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>125494564</v>
+        <v>125494799</v>
       </c>
       <c r="B31" t="n">
-        <v>95873</v>
+        <v>58272</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3750,41 +3732,50 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>2180</v>
+        <v>103042</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Grönfink</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Chloris chloris</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="P31" t="inlineStr">
         <is>
           <t>Stora Saltvik, Stora Saltvik, Sm</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>590606</v>
+        <v>590514</v>
       </c>
       <c r="R31" t="n">
-        <v>6353535</v>
+        <v>6353595</v>
       </c>
       <c r="S31" t="n">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -3840,10 +3831,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>125494897</v>
+        <v>125494786</v>
       </c>
       <c r="B32" t="n">
-        <v>57632</v>
+        <v>57914</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -3856,28 +3847,24 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>100049</v>
+        <v>103012</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Grönsångare</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Phylloscopus sibilatrix</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Bechstein, 1793)</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
       <c r="M32" t="inlineStr">
         <is>
           <t>spel/sång</t>
@@ -3885,17 +3872,17 @@
       </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Skogstorpet  Lilla Saltvik, Saltvik, Sm</t>
+          <t>Stora Saltvik, Stora Saltvik, Sm</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>590484</v>
+        <v>590523</v>
       </c>
       <c r="R32" t="n">
-        <v>6353599</v>
+        <v>6353580</v>
       </c>
       <c r="S32" t="n">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -3951,10 +3938,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>125494037</v>
+        <v>125494897</v>
       </c>
       <c r="B33" t="n">
-        <v>57914</v>
+        <v>57632</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -3967,21 +3954,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>103012</v>
+        <v>100049</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Grönsångare</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Phylloscopus sibilatrix</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Bechstein, 1793)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
@@ -3996,17 +3983,17 @@
       </c>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Stora Saltvik, Stora Saltvik, Sm</t>
+          <t>Skogstorpet  Lilla Saltvik, Saltvik, Sm</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>590499</v>
+        <v>590484</v>
       </c>
       <c r="R33" t="n">
-        <v>6353442</v>
+        <v>6353599</v>
       </c>
       <c r="S33" t="n">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4062,7 +4049,7 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>125494786</v>
+        <v>125494689</v>
       </c>
       <c r="B34" t="n">
         <v>57914</v>
@@ -4095,7 +4082,11 @@
           <t>(Bechstein, 1793)</t>
         </is>
       </c>
-      <c r="I34" t="inlineStr"/>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="M34" t="inlineStr">
         <is>
           <t>spel/sång</t>
@@ -4107,13 +4098,13 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>590523</v>
+        <v>590606</v>
       </c>
       <c r="R34" t="n">
-        <v>6353580</v>
+        <v>6353535</v>
       </c>
       <c r="S34" t="n">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4169,10 +4160,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>125495258</v>
+        <v>125494037</v>
       </c>
       <c r="B35" t="n">
-        <v>95873</v>
+        <v>57914</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4181,41 +4172,50 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>2180</v>
+        <v>103012</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Grönsångare</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Phylloscopus sibilatrix</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr"/>
+          <t>(Bechstein, 1793)</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Skogstorpet  Lilla Saltvik, Skogstorpet  Lilla Saltvik, Sm</t>
+          <t>Stora Saltvik, Stora Saltvik, Sm</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>590493</v>
+        <v>590499</v>
       </c>
       <c r="R35" t="n">
-        <v>6353535</v>
+        <v>6353442</v>
       </c>
       <c r="S35" t="n">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>

--- a/artfynd/A 19260-2025 artfynd.xlsx
+++ b/artfynd/A 19260-2025 artfynd.xlsx
@@ -2775,10 +2775,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>125267309</v>
+        <v>125265231</v>
       </c>
       <c r="B22" t="n">
-        <v>58111</v>
+        <v>95873</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2787,50 +2787,41 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>103018</v>
+        <v>2180</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Svartvit flugsnappare</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Ficedula hypoleuca</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Pallas, 1764)</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
+          <t>(Hedw.) Ångstr.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
           <t>Stora Saltvik, Stora Saltvik, Sm</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>590681</v>
+        <v>590703</v>
       </c>
       <c r="R22" t="n">
-        <v>6353540</v>
+        <v>6353508</v>
       </c>
       <c r="S22" t="n">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -2886,10 +2877,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>125265231</v>
+        <v>125267966</v>
       </c>
       <c r="B23" t="n">
-        <v>95873</v>
+        <v>57914</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2898,41 +2889,50 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>2180</v>
+        <v>103012</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Grönsångare</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Phylloscopus sibilatrix</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr"/>
+          <t>(Bechstein, 1793)</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="P23" t="inlineStr">
         <is>
           <t>Stora Saltvik, Stora Saltvik, Sm</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>590703</v>
+        <v>590812</v>
       </c>
       <c r="R23" t="n">
-        <v>6353508</v>
+        <v>6353560</v>
       </c>
       <c r="S23" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -2988,10 +2988,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>125267966</v>
+        <v>125267309</v>
       </c>
       <c r="B24" t="n">
-        <v>57914</v>
+        <v>58111</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3004,21 +3004,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>103012</v>
+        <v>103018</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Grönsångare</t>
+          <t>Svartvit flugsnappare</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Phylloscopus sibilatrix</t>
+          <t>Ficedula hypoleuca</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Bechstein, 1793)</t>
+          <t>(Pallas, 1764)</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
@@ -3037,13 +3037,13 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>590812</v>
+        <v>590681</v>
       </c>
       <c r="R24" t="n">
-        <v>6353560</v>
+        <v>6353540</v>
       </c>
       <c r="S24" t="n">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>

--- a/artfynd/A 19260-2025 artfynd.xlsx
+++ b/artfynd/A 19260-2025 artfynd.xlsx
@@ -2256,10 +2256,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>125267219</v>
+        <v>125265482</v>
       </c>
       <c r="B17" t="n">
-        <v>95873</v>
+        <v>58111</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2268,41 +2268,50 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>2180</v>
+        <v>103018</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Svartvit flugsnappare</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Ficedula hypoleuca</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr"/>
+          <t>(Pallas, 1764)</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Stora Saltvik, Stora Saltvik, Sm</t>
+          <t>Stora Saltvik, Saltvik, Sm</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>590681</v>
+        <v>590703</v>
       </c>
       <c r="R17" t="n">
-        <v>6353540</v>
+        <v>6353508</v>
       </c>
       <c r="S17" t="n">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2358,10 +2367,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>125265482</v>
+        <v>125267219</v>
       </c>
       <c r="B18" t="n">
-        <v>58111</v>
+        <v>95873</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2370,50 +2379,41 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>103018</v>
+        <v>2180</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Svartvit flugsnappare</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Ficedula hypoleuca</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Pallas, 1764)</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
+          <t>(Hedw.) Ångstr.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Stora Saltvik, Saltvik, Sm</t>
+          <t>Stora Saltvik, Stora Saltvik, Sm</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>590703</v>
+        <v>590681</v>
       </c>
       <c r="R18" t="n">
-        <v>6353508</v>
+        <v>6353540</v>
       </c>
       <c r="S18" t="n">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>

--- a/artfynd/A 19260-2025 artfynd.xlsx
+++ b/artfynd/A 19260-2025 artfynd.xlsx
@@ -675,37 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>125265722</v>
+        <v>125264768</v>
       </c>
       <c r="B2" t="n">
-        <v>95873</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58129</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>2180</v>
+        <v>103018</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Svartvit flugsnappare</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Ficedula hypoleuca</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(Pallas, 1764)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,13 +710,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>590620</v>
+        <v>590735</v>
       </c>
       <c r="R2" t="n">
-        <v>6353512</v>
+        <v>6353466</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -765,27 +760,22 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>125265047</v>
+        <v>125267309</v>
       </c>
       <c r="B3" t="n">
-        <v>57632</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58129</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -793,37 +783,46 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100049</v>
+        <v>103018</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Svartvit flugsnappare</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Ficedula hypoleuca</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
+          <t>(Pallas, 1764)</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Stora Saltvik, Stora Saltvik, Sm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>590693</v>
+        <v>590681</v>
       </c>
       <c r="R3" t="n">
-        <v>6353472</v>
+        <v>6353540</v>
       </c>
       <c r="S3" t="n">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -853,11 +852,6 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-05-20</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Födosökshack</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -872,57 +866,47 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>125266294</v>
+        <v>125266788</v>
       </c>
       <c r="B4" t="n">
-        <v>58111</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>95927</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>103018</v>
+        <v>2180</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Svartvit flugsnappare</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Ficedula hypoleuca</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Pallas, 1764)</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Stora Saltvik, Stora Saltvik, Sm</t>
@@ -935,7 +919,7 @@
         <v>6353534</v>
       </c>
       <c r="S4" t="n">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -991,62 +975,48 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>125264864</v>
+        <v>125265456</v>
       </c>
       <c r="B5" t="n">
-        <v>58111</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>95927</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>103018</v>
+        <v>2180</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Svartvit flugsnappare</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Ficedula hypoleuca</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Pallas, 1764)</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>par i lämplig häckbiotop</t>
-        </is>
-      </c>
+          <t>(Hedw.) Ångstr.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Stora Saltvik, Stora Saltvik, Sm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>590744</v>
+        <v>590690</v>
       </c>
       <c r="R5" t="n">
-        <v>6353445</v>
+        <v>6353521</v>
       </c>
       <c r="S5" t="n">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1090,27 +1060,22 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>125268075</v>
+        <v>125267890</v>
       </c>
       <c r="B6" t="n">
-        <v>58065</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57648</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1118,21 +1083,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>102999</v>
+        <v>100049</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Björktrast</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Turdus pilaris</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -1142,7 +1107,7 @@
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>upprörd, varnande</t>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -1151,13 +1116,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>590840</v>
+        <v>590812</v>
       </c>
       <c r="R6" t="n">
-        <v>6353566</v>
+        <v>6353560</v>
       </c>
       <c r="S6" t="n">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1213,37 +1178,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>125265228</v>
+        <v>125265546</v>
       </c>
       <c r="B7" t="n">
-        <v>79565</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>95927</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6453</v>
+        <v>2180</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1253,13 +1213,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>590685</v>
+        <v>590707</v>
       </c>
       <c r="R7" t="n">
-        <v>6353472</v>
+        <v>6353533</v>
       </c>
       <c r="S7" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1315,15 +1275,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>125265888</v>
+        <v>125267966</v>
       </c>
       <c r="B8" t="n">
-        <v>57632</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57932</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1331,34 +1286,43 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100049</v>
+        <v>103012</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Grönsångare</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Phylloscopus sibilatrix</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
+          <t>(Bechstein, 1793)</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Stora Saltvik, Stora Saltvik, Sm</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>590717</v>
+        <v>590812</v>
       </c>
       <c r="R8" t="n">
-        <v>6353617</v>
+        <v>6353560</v>
       </c>
       <c r="S8" t="n">
         <v>20</v>
@@ -1393,11 +1357,6 @@
           <t>2025-05-20</t>
         </is>
       </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Födosökshack</t>
-        </is>
-      </c>
       <c r="AD8" t="b">
         <v>0</v>
       </c>
@@ -1410,27 +1369,22 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>125267873</v>
+        <v>125268075</v>
       </c>
       <c r="B9" t="n">
-        <v>91186</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58083</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1438,37 +1392,46 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>5442</v>
+        <v>102999</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Björktrast</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Turdus pilaris</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Stora Saltvik, Stora Saltvik, Sm</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>590814</v>
+        <v>590840</v>
       </c>
       <c r="R9" t="n">
-        <v>6353563</v>
+        <v>6353566</v>
       </c>
       <c r="S9" t="n">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1524,62 +1487,48 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>125265536</v>
+        <v>125267022</v>
       </c>
       <c r="B10" t="n">
-        <v>56949</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79585</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100065</v>
+        <v>6453</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Trana</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Grus grus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>Stora Saltvik, Stora Saltvik, Sm</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>590703</v>
+        <v>590681</v>
       </c>
       <c r="R10" t="n">
-        <v>6353508</v>
+        <v>6353540</v>
       </c>
       <c r="S10" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1635,15 +1584,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>125266422</v>
+        <v>125265667</v>
       </c>
       <c r="B11" t="n">
-        <v>95873</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>95927</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1675,10 +1619,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>590574</v>
+        <v>590705</v>
       </c>
       <c r="R11" t="n">
-        <v>6353534</v>
+        <v>6353579</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1725,12 +1669,12 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
@@ -1740,12 +1684,7 @@
         <v>125268245</v>
       </c>
       <c r="B12" t="n">
-        <v>57914</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57932</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1839,62 +1778,48 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>125267890</v>
+        <v>125265040</v>
       </c>
       <c r="B13" t="n">
-        <v>57632</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>95927</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100049</v>
+        <v>2180</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
+          <t>(Hedw.) Ångstr.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>Stora Saltvik, Stora Saltvik, Sm</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>590812</v>
+        <v>590703</v>
       </c>
       <c r="R13" t="n">
-        <v>6353560</v>
+        <v>6353508</v>
       </c>
       <c r="S13" t="n">
-        <v>40</v>
+        <v>10</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1950,53 +1875,57 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>125264768</v>
+        <v>125265536</v>
       </c>
       <c r="B14" t="n">
-        <v>58111</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>56958</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>103018</v>
+        <v>100065</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Svartvit flugsnappare</t>
+          <t>Trana</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Ficedula hypoleuca</t>
+          <t>Grus grus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Pallas, 1764)</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
           <t>Stora Saltvik, Stora Saltvik, Sm</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>590735</v>
+        <v>590703</v>
       </c>
       <c r="R14" t="n">
-        <v>6353466</v>
+        <v>6353508</v>
       </c>
       <c r="S14" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2040,49 +1969,44 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>125268044</v>
+        <v>125267873</v>
       </c>
       <c r="B15" t="n">
-        <v>95873</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91240</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>2180</v>
+        <v>5442</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2092,10 +2016,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>590840</v>
+        <v>590814</v>
       </c>
       <c r="R15" t="n">
-        <v>6353566</v>
+        <v>6353563</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2154,53 +2078,57 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>125264931</v>
+        <v>125264864</v>
       </c>
       <c r="B16" t="n">
-        <v>95591</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58129</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>2671</v>
+        <v>103018</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Fällmossa</t>
+          <t>Svartvit flugsnappare</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Antitrichia curtipendula</t>
+          <t>Ficedula hypoleuca</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Hedw.) Brid.</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr"/>
+          <t>(Pallas, 1764)</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>par i lämplig häckbiotop</t>
+        </is>
+      </c>
       <c r="P16" t="inlineStr">
         <is>
           <t>Stora Saltvik, Stora Saltvik, Sm</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>590731</v>
+        <v>590744</v>
       </c>
       <c r="R16" t="n">
-        <v>6353465</v>
+        <v>6353445</v>
       </c>
       <c r="S16" t="n">
-        <v>15</v>
+        <v>30</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2244,27 +2172,22 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>125265482</v>
+        <v>125266294</v>
       </c>
       <c r="B17" t="n">
-        <v>58111</v>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58129</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2289,11 +2212,7 @@
           <t>(Pallas, 1764)</t>
         </is>
       </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="I17" t="inlineStr"/>
       <c r="M17" t="inlineStr">
         <is>
           <t>spel/sång</t>
@@ -2301,14 +2220,14 @@
       </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Stora Saltvik, Saltvik, Sm</t>
+          <t>Stora Saltvik, Stora Saltvik, Sm</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>590703</v>
+        <v>590574</v>
       </c>
       <c r="R17" t="n">
-        <v>6353508</v>
+        <v>6353534</v>
       </c>
       <c r="S17" t="n">
         <v>30</v>
@@ -2367,15 +2286,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>125267219</v>
+        <v>125268044</v>
       </c>
       <c r="B18" t="n">
-        <v>95873</v>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>95927</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2407,10 +2321,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>590681</v>
+        <v>590840</v>
       </c>
       <c r="R18" t="n">
-        <v>6353540</v>
+        <v>6353566</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2469,37 +2383,32 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>125265546</v>
+        <v>125265228</v>
       </c>
       <c r="B19" t="n">
-        <v>95873</v>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79585</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>2180</v>
+        <v>6453</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2509,13 +2418,13 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>590707</v>
+        <v>590685</v>
       </c>
       <c r="R19" t="n">
-        <v>6353533</v>
+        <v>6353472</v>
       </c>
       <c r="S19" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2571,15 +2480,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>125265456</v>
+        <v>125265581</v>
       </c>
       <c r="B20" t="n">
-        <v>95873</v>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>95927</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2611,13 +2515,13 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>590690</v>
+        <v>590620</v>
       </c>
       <c r="R20" t="n">
-        <v>6353521</v>
+        <v>6353512</v>
       </c>
       <c r="S20" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2661,65 +2565,60 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>125264737</v>
+        <v>125264931</v>
       </c>
       <c r="B21" t="n">
-        <v>57914</v>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>95645</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>103012</v>
+        <v>2671</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Grönsångare</t>
+          <t>Fällmossa</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Phylloscopus sibilatrix</t>
+          <t>Antitrichia curtipendula</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Bechstein, 1793)</t>
+          <t>(Hedw.) Brid.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Stora Saltvik, Saltvik, Sm</t>
+          <t>Stora Saltvik, Stora Saltvik, Sm</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>590732</v>
+        <v>590731</v>
       </c>
       <c r="R21" t="n">
-        <v>6353436</v>
+        <v>6353465</v>
       </c>
       <c r="S21" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2775,43 +2674,47 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>125265231</v>
+        <v>125265482</v>
       </c>
       <c r="B22" t="n">
-        <v>95873</v>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58129</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>2180</v>
+        <v>103018</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Svartvit flugsnappare</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Ficedula hypoleuca</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr"/>
+          <t>(Pallas, 1764)</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Stora Saltvik, Stora Saltvik, Sm</t>
+          <t>Stora Saltvik, Saltvik, Sm</t>
         </is>
       </c>
       <c r="Q22" t="n">
@@ -2821,7 +2724,7 @@
         <v>6353508</v>
       </c>
       <c r="S22" t="n">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -2877,62 +2780,48 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>125267966</v>
+        <v>125267219</v>
       </c>
       <c r="B23" t="n">
-        <v>57914</v>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>95927</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>103012</v>
+        <v>2180</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Grönsångare</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Phylloscopus sibilatrix</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Bechstein, 1793)</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
+          <t>(Hedw.) Ångstr.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
           <t>Stora Saltvik, Stora Saltvik, Sm</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>590812</v>
+        <v>590681</v>
       </c>
       <c r="R23" t="n">
-        <v>6353560</v>
+        <v>6353540</v>
       </c>
       <c r="S23" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -2988,15 +2877,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>125267309</v>
+        <v>125264737</v>
       </c>
       <c r="B24" t="n">
-        <v>58111</v>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57932</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3004,46 +2888,37 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>103018</v>
+        <v>103012</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Svartvit flugsnappare</t>
+          <t>Grönsångare</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Ficedula hypoleuca</t>
+          <t>Phylloscopus sibilatrix</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Pallas, 1764)</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M24" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
+          <t>(Bechstein, 1793)</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Stora Saltvik, Stora Saltvik, Sm</t>
+          <t>Stora Saltvik, Saltvik, Sm</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>590681</v>
+        <v>590732</v>
       </c>
       <c r="R24" t="n">
-        <v>6353540</v>
+        <v>6353436</v>
       </c>
       <c r="S24" t="n">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3087,27 +2962,22 @@
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>125267022</v>
+        <v>125265888</v>
       </c>
       <c r="B25" t="n">
-        <v>79565</v>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57648</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3115,21 +2985,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6453</v>
+        <v>100049</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3139,13 +3009,13 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>590681</v>
+        <v>590717</v>
       </c>
       <c r="R25" t="n">
-        <v>6353540</v>
+        <v>6353617</v>
       </c>
       <c r="S25" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3175,6 +3045,11 @@
       <c r="AA25" t="inlineStr">
         <is>
           <t>2025-05-20</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>Födosökshack</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3189,49 +3064,44 @@
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>125265667</v>
+        <v>125265047</v>
       </c>
       <c r="B26" t="n">
-        <v>95873</v>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57648</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>2180</v>
+        <v>100049</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3241,13 +3111,13 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>590705</v>
+        <v>590693</v>
       </c>
       <c r="R26" t="n">
-        <v>6353579</v>
+        <v>6353472</v>
       </c>
       <c r="S26" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3277,6 +3147,11 @@
       <c r="AA26" t="inlineStr">
         <is>
           <t>2025-05-20</t>
+        </is>
+      </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>Födosökshack</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3303,62 +3178,48 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>125495192</v>
+        <v>125494564</v>
       </c>
       <c r="B27" t="n">
-        <v>57914</v>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>95927</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>103012</v>
+        <v>2180</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Grönsångare</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Phylloscopus sibilatrix</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Bechstein, 1793)</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M27" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
+          <t>(Hedw.) Ångstr.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Skogstorpet  Lilla Saltvik, Skogstorpet  Lilla Saltvik, Sm</t>
+          <t>Stora Saltvik, Stora Saltvik, Sm</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>590493</v>
+        <v>590606</v>
       </c>
       <c r="R27" t="n">
         <v>6353535</v>
       </c>
       <c r="S27" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3414,15 +3275,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>125495143</v>
+        <v>125495258</v>
       </c>
       <c r="B28" t="n">
-        <v>95873</v>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>95927</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3454,10 +3310,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>590497</v>
+        <v>590493</v>
       </c>
       <c r="R28" t="n">
-        <v>6353564</v>
+        <v>6353535</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3516,15 +3372,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>125494564</v>
+        <v>125495143</v>
       </c>
       <c r="B29" t="n">
-        <v>95873</v>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>95927</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3552,14 +3403,14 @@
       <c r="I29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Stora Saltvik, Stora Saltvik, Sm</t>
+          <t>Skogstorpet  Lilla Saltvik, Skogstorpet  Lilla Saltvik, Sm</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>590606</v>
+        <v>590497</v>
       </c>
       <c r="R29" t="n">
-        <v>6353535</v>
+        <v>6353564</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3618,53 +3469,53 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>125495258</v>
+        <v>125494786</v>
       </c>
       <c r="B30" t="n">
-        <v>95873</v>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57932</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>2180</v>
+        <v>103012</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Grönsångare</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Phylloscopus sibilatrix</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(Bechstein, 1793)</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Skogstorpet  Lilla Saltvik, Skogstorpet  Lilla Saltvik, Sm</t>
+          <t>Stora Saltvik, Stora Saltvik, Sm</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>590493</v>
+        <v>590523</v>
       </c>
       <c r="R30" t="n">
-        <v>6353535</v>
+        <v>6353580</v>
       </c>
       <c r="S30" t="n">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -3720,37 +3571,32 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>125494799</v>
+        <v>125494037</v>
       </c>
       <c r="B31" t="n">
-        <v>58272</v>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57932</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>103042</v>
+        <v>103012</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Grönfink</t>
+          <t>Grönsångare</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Chloris chloris</t>
+          <t>Phylloscopus sibilatrix</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Bechstein, 1793)</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
@@ -3769,10 +3615,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>590514</v>
+        <v>590499</v>
       </c>
       <c r="R31" t="n">
-        <v>6353595</v>
+        <v>6353442</v>
       </c>
       <c r="S31" t="n">
         <v>30</v>
@@ -3831,15 +3677,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>125494786</v>
+        <v>125494689</v>
       </c>
       <c r="B32" t="n">
-        <v>57914</v>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57932</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3864,7 +3705,11 @@
           <t>(Bechstein, 1793)</t>
         </is>
       </c>
-      <c r="I32" t="inlineStr"/>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="M32" t="inlineStr">
         <is>
           <t>spel/sång</t>
@@ -3876,13 +3721,13 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>590523</v>
+        <v>590606</v>
       </c>
       <c r="R32" t="n">
-        <v>6353580</v>
+        <v>6353535</v>
       </c>
       <c r="S32" t="n">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -3938,15 +3783,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>125494897</v>
+        <v>125495192</v>
       </c>
       <c r="B33" t="n">
-        <v>57632</v>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57932</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3954,21 +3794,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>100049</v>
+        <v>103012</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Grönsångare</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Phylloscopus sibilatrix</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Bechstein, 1793)</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
@@ -3983,17 +3823,17 @@
       </c>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Skogstorpet  Lilla Saltvik, Saltvik, Sm</t>
+          <t>Skogstorpet  Lilla Saltvik, Skogstorpet  Lilla Saltvik, Sm</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>590484</v>
+        <v>590493</v>
       </c>
       <c r="R33" t="n">
-        <v>6353599</v>
+        <v>6353535</v>
       </c>
       <c r="S33" t="n">
-        <v>40</v>
+        <v>20</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4049,15 +3889,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>125494689</v>
+        <v>125494897</v>
       </c>
       <c r="B34" t="n">
-        <v>57914</v>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57648</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4065,21 +3900,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>103012</v>
+        <v>100049</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Grönsångare</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Phylloscopus sibilatrix</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Bechstein, 1793)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
@@ -4094,14 +3929,14 @@
       </c>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Stora Saltvik, Stora Saltvik, Sm</t>
+          <t>Skogstorpet  Lilla Saltvik, Saltvik, Sm</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>590606</v>
+        <v>590484</v>
       </c>
       <c r="R34" t="n">
-        <v>6353535</v>
+        <v>6353599</v>
       </c>
       <c r="S34" t="n">
         <v>40</v>
@@ -4160,37 +3995,32 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>125494037</v>
+        <v>125494799</v>
       </c>
       <c r="B35" t="n">
-        <v>57914</v>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58291</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>103012</v>
+        <v>103042</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Grönsångare</t>
+          <t>Grönfink</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Phylloscopus sibilatrix</t>
+          <t>Chloris chloris</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Bechstein, 1793)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
@@ -4209,10 +4039,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>590499</v>
+        <v>590514</v>
       </c>
       <c r="R35" t="n">
-        <v>6353442</v>
+        <v>6353595</v>
       </c>
       <c r="S35" t="n">
         <v>30</v>

--- a/artfynd/A 19260-2025 artfynd.xlsx
+++ b/artfynd/A 19260-2025 artfynd.xlsx
@@ -1875,42 +1875,42 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>125265536</v>
+        <v>125264864</v>
       </c>
       <c r="B14" t="n">
-        <v>56958</v>
+        <v>58129</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100065</v>
+        <v>103018</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Trana</t>
+          <t>Svartvit flugsnappare</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Grus grus</t>
+          <t>Ficedula hypoleuca</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Pallas, 1764)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>par i lämplig häckbiotop</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
@@ -1919,13 +1919,13 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>590703</v>
+        <v>590744</v>
       </c>
       <c r="R14" t="n">
-        <v>6353508</v>
+        <v>6353445</v>
       </c>
       <c r="S14" t="n">
-        <v>50</v>
+        <v>30</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -1981,48 +1981,57 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>125267873</v>
+        <v>125265536</v>
       </c>
       <c r="B15" t="n">
-        <v>91240</v>
+        <v>56958</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>5442</v>
+        <v>100065</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Trana</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Grus grus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="P15" t="inlineStr">
         <is>
           <t>Stora Saltvik, Stora Saltvik, Sm</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>590814</v>
+        <v>590703</v>
       </c>
       <c r="R15" t="n">
-        <v>6353563</v>
+        <v>6353508</v>
       </c>
       <c r="S15" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2078,10 +2087,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>125264864</v>
+        <v>125267873</v>
       </c>
       <c r="B16" t="n">
-        <v>58129</v>
+        <v>91240</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2089,46 +2098,37 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>103018</v>
+        <v>5442</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Svartvit flugsnappare</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Ficedula hypoleuca</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Pallas, 1764)</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>par i lämplig häckbiotop</t>
-        </is>
-      </c>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
           <t>Stora Saltvik, Stora Saltvik, Sm</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>590744</v>
+        <v>590814</v>
       </c>
       <c r="R16" t="n">
-        <v>6353445</v>
+        <v>6353563</v>
       </c>
       <c r="S16" t="n">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2877,10 +2877,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>125264737</v>
+        <v>125265888</v>
       </c>
       <c r="B24" t="n">
-        <v>57932</v>
+        <v>57648</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2888,37 +2888,37 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>103012</v>
+        <v>100049</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Grönsångare</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Phylloscopus sibilatrix</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Bechstein, 1793)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Stora Saltvik, Saltvik, Sm</t>
+          <t>Stora Saltvik, Stora Saltvik, Sm</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>590732</v>
+        <v>590717</v>
       </c>
       <c r="R24" t="n">
-        <v>6353436</v>
+        <v>6353617</v>
       </c>
       <c r="S24" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -2948,6 +2948,11 @@
       <c r="AA24" t="inlineStr">
         <is>
           <t>2025-05-20</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>Födosökshack</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -2974,10 +2979,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>125265888</v>
+        <v>125264737</v>
       </c>
       <c r="B25" t="n">
-        <v>57648</v>
+        <v>57932</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2985,37 +2990,37 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>100049</v>
+        <v>103012</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Grönsångare</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Phylloscopus sibilatrix</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Bechstein, 1793)</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Stora Saltvik, Stora Saltvik, Sm</t>
+          <t>Stora Saltvik, Saltvik, Sm</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>590717</v>
+        <v>590732</v>
       </c>
       <c r="R25" t="n">
-        <v>6353617</v>
+        <v>6353436</v>
       </c>
       <c r="S25" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3045,11 +3050,6 @@
       <c r="AA25" t="inlineStr">
         <is>
           <t>2025-05-20</t>
-        </is>
-      </c>
-      <c r="AC25" t="inlineStr">
-        <is>
-          <t>Födosökshack</t>
         </is>
       </c>
       <c r="AD25" t="b">

--- a/artfynd/A 19260-2025 artfynd.xlsx
+++ b/artfynd/A 19260-2025 artfynd.xlsx
@@ -881,7 +881,7 @@
         <v>125266788</v>
       </c>
       <c r="B4" t="n">
-        <v>95927</v>
+        <v>95934</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -978,7 +978,7 @@
         <v>125265456</v>
       </c>
       <c r="B5" t="n">
-        <v>95927</v>
+        <v>95934</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1072,57 +1072,48 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>125267890</v>
+        <v>125265546</v>
       </c>
       <c r="B6" t="n">
-        <v>57648</v>
+        <v>95934</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100049</v>
+        <v>2180</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
+          <t>(Hedw.) Ångstr.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Stora Saltvik, Stora Saltvik, Sm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>590812</v>
+        <v>590707</v>
       </c>
       <c r="R6" t="n">
-        <v>6353560</v>
+        <v>6353533</v>
       </c>
       <c r="S6" t="n">
-        <v>40</v>
+        <v>15</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1166,60 +1157,69 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>125265546</v>
+        <v>125267890</v>
       </c>
       <c r="B7" t="n">
-        <v>95927</v>
+        <v>57648</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>2180</v>
+        <v>100049</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Stora Saltvik, Stora Saltvik, Sm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>590707</v>
+        <v>590812</v>
       </c>
       <c r="R7" t="n">
-        <v>6353533</v>
+        <v>6353560</v>
       </c>
       <c r="S7" t="n">
-        <v>15</v>
+        <v>40</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1263,12 +1263,12 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
@@ -1381,57 +1381,48 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>125268075</v>
+        <v>125265667</v>
       </c>
       <c r="B9" t="n">
-        <v>58083</v>
+        <v>95934</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>102999</v>
+        <v>2180</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Björktrast</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Turdus pilaris</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
+          <t>(Hedw.) Ångstr.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Stora Saltvik, Stora Saltvik, Sm</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>590840</v>
+        <v>590705</v>
       </c>
       <c r="R9" t="n">
-        <v>6353566</v>
+        <v>6353579</v>
       </c>
       <c r="S9" t="n">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1475,12 +1466,12 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
@@ -1584,48 +1575,48 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>125265667</v>
+        <v>125268245</v>
       </c>
       <c r="B11" t="n">
-        <v>95927</v>
+        <v>57932</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>2180</v>
+        <v>103012</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Grönsångare</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Phylloscopus sibilatrix</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(Bechstein, 1793)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Stora Saltvik, Stora Saltvik, Sm</t>
+          <t>Lerbro, Lerbro, Sm</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>590705</v>
+        <v>590069</v>
       </c>
       <c r="R11" t="n">
-        <v>6353579</v>
+        <v>6353421</v>
       </c>
       <c r="S11" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1681,10 +1672,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>125268245</v>
+        <v>125268075</v>
       </c>
       <c r="B12" t="n">
-        <v>57932</v>
+        <v>58083</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1692,37 +1683,46 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>103012</v>
+        <v>102999</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Grönsångare</t>
+          <t>Björktrast</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Phylloscopus sibilatrix</t>
+          <t>Turdus pilaris</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Bechstein, 1793)</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Lerbro, Lerbro, Sm</t>
+          <t>Stora Saltvik, Stora Saltvik, Sm</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>590069</v>
+        <v>590840</v>
       </c>
       <c r="R12" t="n">
-        <v>6353421</v>
+        <v>6353566</v>
       </c>
       <c r="S12" t="n">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1766,12 +1766,12 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
@@ -1781,7 +1781,7 @@
         <v>125265040</v>
       </c>
       <c r="B13" t="n">
-        <v>95927</v>
+        <v>95934</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1875,10 +1875,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>125264864</v>
+        <v>125267873</v>
       </c>
       <c r="B14" t="n">
-        <v>58129</v>
+        <v>91247</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1886,46 +1886,37 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>103018</v>
+        <v>5442</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Svartvit flugsnappare</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Ficedula hypoleuca</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Pallas, 1764)</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>par i lämplig häckbiotop</t>
-        </is>
-      </c>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
           <t>Stora Saltvik, Stora Saltvik, Sm</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>590744</v>
+        <v>590814</v>
       </c>
       <c r="R14" t="n">
-        <v>6353445</v>
+        <v>6353563</v>
       </c>
       <c r="S14" t="n">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -1981,42 +1972,42 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>125265536</v>
+        <v>125264864</v>
       </c>
       <c r="B15" t="n">
-        <v>56958</v>
+        <v>58129</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100065</v>
+        <v>103018</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Trana</t>
+          <t>Svartvit flugsnappare</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Grus grus</t>
+          <t>Ficedula hypoleuca</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Pallas, 1764)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>par i lämplig häckbiotop</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
@@ -2025,13 +2016,13 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>590703</v>
+        <v>590744</v>
       </c>
       <c r="R15" t="n">
-        <v>6353508</v>
+        <v>6353445</v>
       </c>
       <c r="S15" t="n">
-        <v>50</v>
+        <v>30</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2087,48 +2078,57 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>125267873</v>
+        <v>125265536</v>
       </c>
       <c r="B16" t="n">
-        <v>91240</v>
+        <v>56958</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>5442</v>
+        <v>100065</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Trana</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Grus grus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="P16" t="inlineStr">
         <is>
           <t>Stora Saltvik, Stora Saltvik, Sm</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>590814</v>
+        <v>590703</v>
       </c>
       <c r="R16" t="n">
-        <v>6353563</v>
+        <v>6353508</v>
       </c>
       <c r="S16" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2289,7 +2289,7 @@
         <v>125268044</v>
       </c>
       <c r="B18" t="n">
-        <v>95927</v>
+        <v>95934</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2483,7 +2483,7 @@
         <v>125265581</v>
       </c>
       <c r="B20" t="n">
-        <v>95927</v>
+        <v>95934</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2580,7 +2580,7 @@
         <v>125264931</v>
       </c>
       <c r="B21" t="n">
-        <v>95645</v>
+        <v>95652</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2783,7 +2783,7 @@
         <v>125267219</v>
       </c>
       <c r="B23" t="n">
-        <v>95927</v>
+        <v>95934</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2877,10 +2877,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>125265888</v>
+        <v>125264737</v>
       </c>
       <c r="B24" t="n">
-        <v>57648</v>
+        <v>57932</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2888,37 +2888,37 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>100049</v>
+        <v>103012</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Grönsångare</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Phylloscopus sibilatrix</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Bechstein, 1793)</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Stora Saltvik, Stora Saltvik, Sm</t>
+          <t>Stora Saltvik, Saltvik, Sm</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>590717</v>
+        <v>590732</v>
       </c>
       <c r="R24" t="n">
-        <v>6353617</v>
+        <v>6353436</v>
       </c>
       <c r="S24" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -2948,11 +2948,6 @@
       <c r="AA24" t="inlineStr">
         <is>
           <t>2025-05-20</t>
-        </is>
-      </c>
-      <c r="AC24" t="inlineStr">
-        <is>
-          <t>Födosökshack</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -2979,10 +2974,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>125264737</v>
+        <v>125265888</v>
       </c>
       <c r="B25" t="n">
-        <v>57932</v>
+        <v>57648</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2990,37 +2985,37 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>103012</v>
+        <v>100049</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Grönsångare</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Phylloscopus sibilatrix</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Bechstein, 1793)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Stora Saltvik, Saltvik, Sm</t>
+          <t>Stora Saltvik, Stora Saltvik, Sm</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>590732</v>
+        <v>590717</v>
       </c>
       <c r="R25" t="n">
-        <v>6353436</v>
+        <v>6353617</v>
       </c>
       <c r="S25" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3050,6 +3045,11 @@
       <c r="AA25" t="inlineStr">
         <is>
           <t>2025-05-20</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>Födosökshack</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3181,7 +3181,7 @@
         <v>125494564</v>
       </c>
       <c r="B27" t="n">
-        <v>95927</v>
+        <v>95934</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3278,7 +3278,7 @@
         <v>125495258</v>
       </c>
       <c r="B28" t="n">
-        <v>95927</v>
+        <v>95934</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3375,7 +3375,7 @@
         <v>125495143</v>
       </c>
       <c r="B29" t="n">
-        <v>95927</v>
+        <v>95934</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3783,10 +3783,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>125495192</v>
+        <v>125494897</v>
       </c>
       <c r="B33" t="n">
-        <v>57932</v>
+        <v>57648</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3794,21 +3794,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>103012</v>
+        <v>100049</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Grönsångare</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Phylloscopus sibilatrix</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Bechstein, 1793)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
@@ -3823,17 +3823,17 @@
       </c>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Skogstorpet  Lilla Saltvik, Skogstorpet  Lilla Saltvik, Sm</t>
+          <t>Skogstorpet  Lilla Saltvik, Saltvik, Sm</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>590493</v>
+        <v>590484</v>
       </c>
       <c r="R33" t="n">
-        <v>6353535</v>
+        <v>6353599</v>
       </c>
       <c r="S33" t="n">
-        <v>20</v>
+        <v>40</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -3889,10 +3889,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>125494897</v>
+        <v>125495192</v>
       </c>
       <c r="B34" t="n">
-        <v>57648</v>
+        <v>57932</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3900,21 +3900,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>100049</v>
+        <v>103012</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Grönsångare</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Phylloscopus sibilatrix</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Bechstein, 1793)</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
@@ -3929,17 +3929,17 @@
       </c>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Skogstorpet  Lilla Saltvik, Saltvik, Sm</t>
+          <t>Skogstorpet  Lilla Saltvik, Skogstorpet  Lilla Saltvik, Sm</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>590484</v>
+        <v>590493</v>
       </c>
       <c r="R34" t="n">
-        <v>6353599</v>
+        <v>6353535</v>
       </c>
       <c r="S34" t="n">
-        <v>40</v>
+        <v>20</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>

--- a/artfynd/A 19260-2025 artfynd.xlsx
+++ b/artfynd/A 19260-2025 artfynd.xlsx
@@ -1575,10 +1575,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>125268245</v>
+        <v>125268075</v>
       </c>
       <c r="B11" t="n">
-        <v>57932</v>
+        <v>58083</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1586,37 +1586,46 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>103012</v>
+        <v>102999</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Grönsångare</t>
+          <t>Björktrast</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Phylloscopus sibilatrix</t>
+          <t>Turdus pilaris</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Bechstein, 1793)</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Lerbro, Lerbro, Sm</t>
+          <t>Stora Saltvik, Stora Saltvik, Sm</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>590069</v>
+        <v>590840</v>
       </c>
       <c r="R11" t="n">
-        <v>6353421</v>
+        <v>6353566</v>
       </c>
       <c r="S11" t="n">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1660,22 +1669,22 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>125268075</v>
+        <v>125268245</v>
       </c>
       <c r="B12" t="n">
-        <v>58083</v>
+        <v>57932</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1683,46 +1692,37 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>102999</v>
+        <v>103012</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Björktrast</t>
+          <t>Grönsångare</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Turdus pilaris</t>
+          <t>Phylloscopus sibilatrix</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
+          <t>(Bechstein, 1793)</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Stora Saltvik, Stora Saltvik, Sm</t>
+          <t>Lerbro, Lerbro, Sm</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>590840</v>
+        <v>590069</v>
       </c>
       <c r="R12" t="n">
-        <v>6353566</v>
+        <v>6353421</v>
       </c>
       <c r="S12" t="n">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1766,12 +1766,12 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
@@ -1972,42 +1972,42 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>125264864</v>
+        <v>125265536</v>
       </c>
       <c r="B15" t="n">
-        <v>58129</v>
+        <v>56958</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>103018</v>
+        <v>100065</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Svartvit flugsnappare</t>
+          <t>Trana</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Ficedula hypoleuca</t>
+          <t>Grus grus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Pallas, 1764)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>par i lämplig häckbiotop</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
@@ -2016,13 +2016,13 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>590744</v>
+        <v>590703</v>
       </c>
       <c r="R15" t="n">
-        <v>6353445</v>
+        <v>6353508</v>
       </c>
       <c r="S15" t="n">
-        <v>30</v>
+        <v>50</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2078,42 +2078,42 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>125265536</v>
+        <v>125264864</v>
       </c>
       <c r="B16" t="n">
-        <v>56958</v>
+        <v>58129</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100065</v>
+        <v>103018</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Trana</t>
+          <t>Svartvit flugsnappare</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Grus grus</t>
+          <t>Ficedula hypoleuca</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Pallas, 1764)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>par i lämplig häckbiotop</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
@@ -2122,13 +2122,13 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>590703</v>
+        <v>590744</v>
       </c>
       <c r="R16" t="n">
-        <v>6353508</v>
+        <v>6353445</v>
       </c>
       <c r="S16" t="n">
-        <v>50</v>
+        <v>30</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2184,53 +2184,48 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>125266294</v>
+        <v>125268044</v>
       </c>
       <c r="B17" t="n">
-        <v>58129</v>
+        <v>95934</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>103018</v>
+        <v>2180</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Svartvit flugsnappare</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Ficedula hypoleuca</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Pallas, 1764)</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
       <c r="P17" t="inlineStr">
         <is>
           <t>Stora Saltvik, Stora Saltvik, Sm</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>590574</v>
+        <v>590840</v>
       </c>
       <c r="R17" t="n">
-        <v>6353534</v>
+        <v>6353566</v>
       </c>
       <c r="S17" t="n">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2286,48 +2281,53 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>125268044</v>
+        <v>125266294</v>
       </c>
       <c r="B18" t="n">
-        <v>95934</v>
+        <v>58129</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>2180</v>
+        <v>103018</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Svartvit flugsnappare</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Ficedula hypoleuca</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(Pallas, 1764)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="P18" t="inlineStr">
         <is>
           <t>Stora Saltvik, Stora Saltvik, Sm</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>590840</v>
+        <v>590574</v>
       </c>
       <c r="R18" t="n">
-        <v>6353566</v>
+        <v>6353534</v>
       </c>
       <c r="S18" t="n">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>

--- a/artfynd/A 19260-2025 artfynd.xlsx
+++ b/artfynd/A 19260-2025 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>125264768</v>
+        <v>125267309</v>
       </c>
       <c r="B2" t="n">
         <v>58129</v>
@@ -703,20 +703,29 @@
           <t>(Pallas, 1764)</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr"/>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Stora Saltvik, Stora Saltvik, Sm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>590735</v>
+        <v>590681</v>
       </c>
       <c r="R2" t="n">
-        <v>6353466</v>
+        <v>6353540</v>
       </c>
       <c r="S2" t="n">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -760,19 +769,19 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>125267309</v>
+        <v>125264768</v>
       </c>
       <c r="B3" t="n">
         <v>58129</v>
@@ -800,29 +809,20 @@
           <t>(Pallas, 1764)</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Stora Saltvik, Stora Saltvik, Sm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>590681</v>
+        <v>590735</v>
       </c>
       <c r="R3" t="n">
-        <v>6353540</v>
+        <v>6353466</v>
       </c>
       <c r="S3" t="n">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -866,12 +866,12 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
@@ -1972,42 +1972,42 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>125265536</v>
+        <v>125264864</v>
       </c>
       <c r="B15" t="n">
-        <v>56958</v>
+        <v>58129</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100065</v>
+        <v>103018</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Trana</t>
+          <t>Svartvit flugsnappare</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Grus grus</t>
+          <t>Ficedula hypoleuca</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Pallas, 1764)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>par i lämplig häckbiotop</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
@@ -2016,13 +2016,13 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>590703</v>
+        <v>590744</v>
       </c>
       <c r="R15" t="n">
-        <v>6353508</v>
+        <v>6353445</v>
       </c>
       <c r="S15" t="n">
-        <v>50</v>
+        <v>30</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2078,42 +2078,42 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>125264864</v>
+        <v>125265536</v>
       </c>
       <c r="B16" t="n">
-        <v>58129</v>
+        <v>56958</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>103018</v>
+        <v>100065</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Svartvit flugsnappare</t>
+          <t>Trana</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Ficedula hypoleuca</t>
+          <t>Grus grus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Pallas, 1764)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>par i lämplig häckbiotop</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
@@ -2122,13 +2122,13 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>590744</v>
+        <v>590703</v>
       </c>
       <c r="R16" t="n">
-        <v>6353445</v>
+        <v>6353508</v>
       </c>
       <c r="S16" t="n">
-        <v>30</v>
+        <v>50</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2184,48 +2184,53 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>125268044</v>
+        <v>125266294</v>
       </c>
       <c r="B17" t="n">
-        <v>95934</v>
+        <v>58129</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>2180</v>
+        <v>103018</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Svartvit flugsnappare</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Ficedula hypoleuca</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(Pallas, 1764)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="P17" t="inlineStr">
         <is>
           <t>Stora Saltvik, Stora Saltvik, Sm</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>590840</v>
+        <v>590574</v>
       </c>
       <c r="R17" t="n">
-        <v>6353566</v>
+        <v>6353534</v>
       </c>
       <c r="S17" t="n">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2281,53 +2286,48 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>125266294</v>
+        <v>125268044</v>
       </c>
       <c r="B18" t="n">
-        <v>58129</v>
+        <v>95934</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>103018</v>
+        <v>2180</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Svartvit flugsnappare</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Ficedula hypoleuca</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Pallas, 1764)</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
       <c r="P18" t="inlineStr">
         <is>
           <t>Stora Saltvik, Stora Saltvik, Sm</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>590574</v>
+        <v>590840</v>
       </c>
       <c r="R18" t="n">
-        <v>6353534</v>
+        <v>6353566</v>
       </c>
       <c r="S18" t="n">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>

--- a/artfynd/A 19260-2025 artfynd.xlsx
+++ b/artfynd/A 19260-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>125267309</v>
+        <v>125264768</v>
       </c>
       <c r="B2" t="n">
-        <v>58129</v>
+        <v>58130</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -703,29 +703,20 @@
           <t>(Pallas, 1764)</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Stora Saltvik, Stora Saltvik, Sm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>590681</v>
+        <v>590735</v>
       </c>
       <c r="R2" t="n">
-        <v>6353540</v>
+        <v>6353466</v>
       </c>
       <c r="S2" t="n">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -769,22 +760,22 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>125264768</v>
+        <v>125267309</v>
       </c>
       <c r="B3" t="n">
-        <v>58129</v>
+        <v>58130</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -809,20 +800,29 @@
           <t>(Pallas, 1764)</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr"/>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Stora Saltvik, Stora Saltvik, Sm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>590735</v>
+        <v>590681</v>
       </c>
       <c r="R3" t="n">
-        <v>6353466</v>
+        <v>6353540</v>
       </c>
       <c r="S3" t="n">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -866,12 +866,12 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
@@ -881,7 +881,7 @@
         <v>125266788</v>
       </c>
       <c r="B4" t="n">
-        <v>95934</v>
+        <v>95937</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -978,7 +978,7 @@
         <v>125265456</v>
       </c>
       <c r="B5" t="n">
-        <v>95934</v>
+        <v>95937</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1075,7 +1075,7 @@
         <v>125265546</v>
       </c>
       <c r="B6" t="n">
-        <v>95934</v>
+        <v>95937</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1278,7 +1278,7 @@
         <v>125267966</v>
       </c>
       <c r="B8" t="n">
-        <v>57932</v>
+        <v>57933</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1381,48 +1381,57 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>125265667</v>
+        <v>125268075</v>
       </c>
       <c r="B9" t="n">
-        <v>95934</v>
+        <v>58084</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>2180</v>
+        <v>102999</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Björktrast</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Turdus pilaris</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Stora Saltvik, Stora Saltvik, Sm</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>590705</v>
+        <v>590840</v>
       </c>
       <c r="R9" t="n">
-        <v>6353579</v>
+        <v>6353566</v>
       </c>
       <c r="S9" t="n">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1466,22 +1475,22 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>125267022</v>
+        <v>125268245</v>
       </c>
       <c r="B10" t="n">
-        <v>79585</v>
+        <v>57933</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1489,37 +1498,37 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6453</v>
+        <v>103012</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Grönsångare</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Phylloscopus sibilatrix</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Bechstein, 1793)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Stora Saltvik, Stora Saltvik, Sm</t>
+          <t>Lerbro, Lerbro, Sm</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>590681</v>
+        <v>590069</v>
       </c>
       <c r="R10" t="n">
-        <v>6353540</v>
+        <v>6353421</v>
       </c>
       <c r="S10" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1563,69 +1572,60 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>125268075</v>
+        <v>125265667</v>
       </c>
       <c r="B11" t="n">
-        <v>58083</v>
+        <v>95937</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>102999</v>
+        <v>2180</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Björktrast</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Turdus pilaris</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
+          <t>(Hedw.) Ångstr.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>Stora Saltvik, Stora Saltvik, Sm</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>590840</v>
+        <v>590705</v>
       </c>
       <c r="R11" t="n">
-        <v>6353566</v>
+        <v>6353579</v>
       </c>
       <c r="S11" t="n">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1669,22 +1669,22 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>125268245</v>
+        <v>125267022</v>
       </c>
       <c r="B12" t="n">
-        <v>57932</v>
+        <v>79586</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1692,37 +1692,37 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>103012</v>
+        <v>6453</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Grönsångare</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Phylloscopus sibilatrix</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Bechstein, 1793)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Lerbro, Lerbro, Sm</t>
+          <t>Stora Saltvik, Stora Saltvik, Sm</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>590069</v>
+        <v>590681</v>
       </c>
       <c r="R12" t="n">
-        <v>6353421</v>
+        <v>6353540</v>
       </c>
       <c r="S12" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1766,12 +1766,12 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
@@ -1781,7 +1781,7 @@
         <v>125265040</v>
       </c>
       <c r="B13" t="n">
-        <v>95934</v>
+        <v>95937</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1875,48 +1875,57 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>125267873</v>
+        <v>125265536</v>
       </c>
       <c r="B14" t="n">
-        <v>91247</v>
+        <v>56958</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>5442</v>
+        <v>100065</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Trana</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Grus grus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
           <t>Stora Saltvik, Stora Saltvik, Sm</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>590814</v>
+        <v>590703</v>
       </c>
       <c r="R14" t="n">
-        <v>6353563</v>
+        <v>6353508</v>
       </c>
       <c r="S14" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -1975,7 +1984,7 @@
         <v>125264864</v>
       </c>
       <c r="B15" t="n">
-        <v>58129</v>
+        <v>58130</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2078,57 +2087,48 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>125265536</v>
+        <v>125267873</v>
       </c>
       <c r="B16" t="n">
-        <v>56958</v>
+        <v>91248</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100065</v>
+        <v>5442</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Trana</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Grus grus</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
           <t>Stora Saltvik, Stora Saltvik, Sm</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>590703</v>
+        <v>590814</v>
       </c>
       <c r="R16" t="n">
-        <v>6353508</v>
+        <v>6353563</v>
       </c>
       <c r="S16" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2187,7 +2187,7 @@
         <v>125266294</v>
       </c>
       <c r="B17" t="n">
-        <v>58129</v>
+        <v>58130</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2289,7 +2289,7 @@
         <v>125268044</v>
       </c>
       <c r="B18" t="n">
-        <v>95934</v>
+        <v>95937</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2386,7 +2386,7 @@
         <v>125265228</v>
       </c>
       <c r="B19" t="n">
-        <v>79585</v>
+        <v>79586</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2483,7 +2483,7 @@
         <v>125265581</v>
       </c>
       <c r="B20" t="n">
-        <v>95934</v>
+        <v>95937</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2580,7 +2580,7 @@
         <v>125264931</v>
       </c>
       <c r="B21" t="n">
-        <v>95652</v>
+        <v>95655</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2677,7 +2677,7 @@
         <v>125265482</v>
       </c>
       <c r="B22" t="n">
-        <v>58129</v>
+        <v>58130</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2783,7 +2783,7 @@
         <v>125267219</v>
       </c>
       <c r="B23" t="n">
-        <v>95934</v>
+        <v>95937</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2880,7 +2880,7 @@
         <v>125264737</v>
       </c>
       <c r="B24" t="n">
-        <v>57932</v>
+        <v>57933</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3181,7 +3181,7 @@
         <v>125494564</v>
       </c>
       <c r="B27" t="n">
-        <v>95934</v>
+        <v>95937</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3278,7 +3278,7 @@
         <v>125495258</v>
       </c>
       <c r="B28" t="n">
-        <v>95934</v>
+        <v>95937</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3375,7 +3375,7 @@
         <v>125495143</v>
       </c>
       <c r="B29" t="n">
-        <v>95934</v>
+        <v>95937</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3472,7 +3472,7 @@
         <v>125494786</v>
       </c>
       <c r="B30" t="n">
-        <v>57932</v>
+        <v>57933</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3574,7 +3574,7 @@
         <v>125494037</v>
       </c>
       <c r="B31" t="n">
-        <v>57932</v>
+        <v>57933</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3680,7 +3680,7 @@
         <v>125494689</v>
       </c>
       <c r="B32" t="n">
-        <v>57932</v>
+        <v>57933</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3892,7 +3892,7 @@
         <v>125495192</v>
       </c>
       <c r="B34" t="n">
-        <v>57932</v>
+        <v>57933</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3998,7 +3998,7 @@
         <v>125494799</v>
       </c>
       <c r="B35" t="n">
-        <v>58291</v>
+        <v>58292</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>

--- a/artfynd/A 19260-2025 artfynd.xlsx
+++ b/artfynd/A 19260-2025 artfynd.xlsx
@@ -3181,7 +3181,7 @@
         <v>125494564</v>
       </c>
       <c r="B27" t="n">
-        <v>95937</v>
+        <v>95941</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3278,7 +3278,7 @@
         <v>125495258</v>
       </c>
       <c r="B28" t="n">
-        <v>95937</v>
+        <v>95941</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3375,7 +3375,7 @@
         <v>125495143</v>
       </c>
       <c r="B29" t="n">
-        <v>95937</v>
+        <v>95941</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3783,10 +3783,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>125494897</v>
+        <v>125495192</v>
       </c>
       <c r="B33" t="n">
-        <v>57648</v>
+        <v>57933</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3794,21 +3794,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>100049</v>
+        <v>103012</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Grönsångare</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Phylloscopus sibilatrix</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Bechstein, 1793)</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
@@ -3823,17 +3823,17 @@
       </c>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Skogstorpet  Lilla Saltvik, Saltvik, Sm</t>
+          <t>Skogstorpet  Lilla Saltvik, Skogstorpet  Lilla Saltvik, Sm</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>590484</v>
+        <v>590493</v>
       </c>
       <c r="R33" t="n">
-        <v>6353599</v>
+        <v>6353535</v>
       </c>
       <c r="S33" t="n">
-        <v>40</v>
+        <v>20</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -3889,10 +3889,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>125495192</v>
+        <v>125494897</v>
       </c>
       <c r="B34" t="n">
-        <v>57933</v>
+        <v>57648</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3900,21 +3900,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>103012</v>
+        <v>100049</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Grönsångare</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Phylloscopus sibilatrix</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Bechstein, 1793)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
@@ -3929,17 +3929,17 @@
       </c>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Skogstorpet  Lilla Saltvik, Skogstorpet  Lilla Saltvik, Sm</t>
+          <t>Skogstorpet  Lilla Saltvik, Saltvik, Sm</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>590493</v>
+        <v>590484</v>
       </c>
       <c r="R34" t="n">
-        <v>6353535</v>
+        <v>6353599</v>
       </c>
       <c r="S34" t="n">
-        <v>20</v>
+        <v>40</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>

--- a/artfynd/A 19260-2025 artfynd.xlsx
+++ b/artfynd/A 19260-2025 artfynd.xlsx
@@ -3181,7 +3181,7 @@
         <v>125494564</v>
       </c>
       <c r="B27" t="n">
-        <v>95941</v>
+        <v>95942</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3278,7 +3278,7 @@
         <v>125495258</v>
       </c>
       <c r="B28" t="n">
-        <v>95941</v>
+        <v>95942</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3375,7 +3375,7 @@
         <v>125495143</v>
       </c>
       <c r="B29" t="n">
-        <v>95941</v>
+        <v>95942</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3783,10 +3783,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>125495192</v>
+        <v>125494897</v>
       </c>
       <c r="B33" t="n">
-        <v>57933</v>
+        <v>57648</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3794,21 +3794,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>103012</v>
+        <v>100049</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Grönsångare</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Phylloscopus sibilatrix</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Bechstein, 1793)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
@@ -3823,17 +3823,17 @@
       </c>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Skogstorpet  Lilla Saltvik, Skogstorpet  Lilla Saltvik, Sm</t>
+          <t>Skogstorpet  Lilla Saltvik, Saltvik, Sm</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>590493</v>
+        <v>590484</v>
       </c>
       <c r="R33" t="n">
-        <v>6353535</v>
+        <v>6353599</v>
       </c>
       <c r="S33" t="n">
-        <v>20</v>
+        <v>40</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -3889,10 +3889,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>125494897</v>
+        <v>125495192</v>
       </c>
       <c r="B34" t="n">
-        <v>57648</v>
+        <v>57933</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3900,21 +3900,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>100049</v>
+        <v>103012</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Grönsångare</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Phylloscopus sibilatrix</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Bechstein, 1793)</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
@@ -3929,17 +3929,17 @@
       </c>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Skogstorpet  Lilla Saltvik, Saltvik, Sm</t>
+          <t>Skogstorpet  Lilla Saltvik, Skogstorpet  Lilla Saltvik, Sm</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>590484</v>
+        <v>590493</v>
       </c>
       <c r="R34" t="n">
-        <v>6353599</v>
+        <v>6353535</v>
       </c>
       <c r="S34" t="n">
-        <v>40</v>
+        <v>20</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>

--- a/artfynd/A 19260-2025 artfynd.xlsx
+++ b/artfynd/A 19260-2025 artfynd.xlsx
@@ -3783,10 +3783,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>125494897</v>
+        <v>125495192</v>
       </c>
       <c r="B33" t="n">
-        <v>57648</v>
+        <v>57933</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3794,21 +3794,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>100049</v>
+        <v>103012</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Grönsångare</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Phylloscopus sibilatrix</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Bechstein, 1793)</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
@@ -3823,17 +3823,17 @@
       </c>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Skogstorpet  Lilla Saltvik, Saltvik, Sm</t>
+          <t>Skogstorpet  Lilla Saltvik, Skogstorpet  Lilla Saltvik, Sm</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>590484</v>
+        <v>590493</v>
       </c>
       <c r="R33" t="n">
-        <v>6353599</v>
+        <v>6353535</v>
       </c>
       <c r="S33" t="n">
-        <v>40</v>
+        <v>20</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -3889,10 +3889,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>125495192</v>
+        <v>125494897</v>
       </c>
       <c r="B34" t="n">
-        <v>57933</v>
+        <v>57648</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3900,21 +3900,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>103012</v>
+        <v>100049</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Grönsångare</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Phylloscopus sibilatrix</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Bechstein, 1793)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
@@ -3929,17 +3929,17 @@
       </c>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Skogstorpet  Lilla Saltvik, Skogstorpet  Lilla Saltvik, Sm</t>
+          <t>Skogstorpet  Lilla Saltvik, Saltvik, Sm</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>590493</v>
+        <v>590484</v>
       </c>
       <c r="R34" t="n">
-        <v>6353535</v>
+        <v>6353599</v>
       </c>
       <c r="S34" t="n">
-        <v>20</v>
+        <v>40</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>

--- a/artfynd/A 19260-2025 artfynd.xlsx
+++ b/artfynd/A 19260-2025 artfynd.xlsx
@@ -3181,7 +3181,7 @@
         <v>125494564</v>
       </c>
       <c r="B27" t="n">
-        <v>95942</v>
+        <v>95944</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3278,7 +3278,7 @@
         <v>125495258</v>
       </c>
       <c r="B28" t="n">
-        <v>95942</v>
+        <v>95944</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3375,7 +3375,7 @@
         <v>125495143</v>
       </c>
       <c r="B29" t="n">
-        <v>95942</v>
+        <v>95944</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3472,7 +3472,7 @@
         <v>125494786</v>
       </c>
       <c r="B30" t="n">
-        <v>57933</v>
+        <v>57934</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3574,7 +3574,7 @@
         <v>125494037</v>
       </c>
       <c r="B31" t="n">
-        <v>57933</v>
+        <v>57934</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3680,7 +3680,7 @@
         <v>125494689</v>
       </c>
       <c r="B32" t="n">
-        <v>57933</v>
+        <v>57934</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3786,7 +3786,7 @@
         <v>125495192</v>
       </c>
       <c r="B33" t="n">
-        <v>57933</v>
+        <v>57934</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3892,7 +3892,7 @@
         <v>125494897</v>
       </c>
       <c r="B34" t="n">
-        <v>57648</v>
+        <v>57649</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3998,7 +3998,7 @@
         <v>125494799</v>
       </c>
       <c r="B35" t="n">
-        <v>58292</v>
+        <v>58293</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>

--- a/artfynd/A 19260-2025 artfynd.xlsx
+++ b/artfynd/A 19260-2025 artfynd.xlsx
@@ -3181,7 +3181,7 @@
         <v>125494564</v>
       </c>
       <c r="B27" t="n">
-        <v>95944</v>
+        <v>95946</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3278,7 +3278,7 @@
         <v>125495258</v>
       </c>
       <c r="B28" t="n">
-        <v>95944</v>
+        <v>95946</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3375,7 +3375,7 @@
         <v>125495143</v>
       </c>
       <c r="B29" t="n">
-        <v>95944</v>
+        <v>95946</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3783,10 +3783,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>125495192</v>
+        <v>125494897</v>
       </c>
       <c r="B33" t="n">
-        <v>57934</v>
+        <v>57649</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3794,21 +3794,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>103012</v>
+        <v>100049</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Grönsångare</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Phylloscopus sibilatrix</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Bechstein, 1793)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
@@ -3823,17 +3823,17 @@
       </c>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Skogstorpet  Lilla Saltvik, Skogstorpet  Lilla Saltvik, Sm</t>
+          <t>Skogstorpet  Lilla Saltvik, Saltvik, Sm</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>590493</v>
+        <v>590484</v>
       </c>
       <c r="R33" t="n">
-        <v>6353535</v>
+        <v>6353599</v>
       </c>
       <c r="S33" t="n">
-        <v>20</v>
+        <v>40</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -3889,10 +3889,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>125494897</v>
+        <v>125495192</v>
       </c>
       <c r="B34" t="n">
-        <v>57649</v>
+        <v>57934</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3900,21 +3900,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>100049</v>
+        <v>103012</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Grönsångare</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Phylloscopus sibilatrix</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Bechstein, 1793)</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
@@ -3929,17 +3929,17 @@
       </c>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Skogstorpet  Lilla Saltvik, Saltvik, Sm</t>
+          <t>Skogstorpet  Lilla Saltvik, Skogstorpet  Lilla Saltvik, Sm</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>590484</v>
+        <v>590493</v>
       </c>
       <c r="R34" t="n">
-        <v>6353599</v>
+        <v>6353535</v>
       </c>
       <c r="S34" t="n">
-        <v>40</v>
+        <v>20</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
